--- a/Module 3/Week 11 - Short sales and dollar-neutral strategies/Example with value and growth stocks.xlsx
+++ b/Module 3/Week 11 - Short sales and dollar-neutral strategies/Example with value and growth stocks.xlsx
@@ -8,9 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="At 1% exc return vol" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="At 1% exc return vol" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -39,13 +39,13 @@
     <t xml:space="preserve">Growth</t>
   </si>
   <si>
-    <t xml:space="preserve">Market exc</t>
+    <t xml:space="preserve">Market excess</t>
   </si>
   <si>
-    <t xml:space="preserve">Value exc</t>
+    <t xml:space="preserve">Value excess</t>
   </si>
   <si>
-    <t xml:space="preserve">Growth exc</t>
+    <t xml:space="preserve">Growth excess</t>
   </si>
   <si>
     <t xml:space="preserve">Value minus growth</t>
@@ -161,7 +161,7 @@
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -191,12 +191,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u val="single"/>
@@ -256,44 +250,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -309,8 +307,114 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -318,43 +422,43 @@
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="10.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="9.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="11.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="18.24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="5" t="n">
         <v>25934</v>
       </c>
       <c r="B2" s="1" t="n">
@@ -387,7 +491,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>25965</v>
       </c>
       <c r="B3" s="1" t="n">
@@ -420,7 +524,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>25993</v>
       </c>
       <c r="B4" s="1" t="n">
@@ -453,7 +557,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>26024</v>
       </c>
       <c r="B5" s="1" t="n">
@@ -486,7 +590,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>26054</v>
       </c>
       <c r="B6" s="1" t="n">
@@ -519,7 +623,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>26085</v>
       </c>
       <c r="B7" s="1" t="n">
@@ -552,7 +656,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>26115</v>
       </c>
       <c r="B8" s="1" t="n">
@@ -585,7 +689,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>26146</v>
       </c>
       <c r="B9" s="1" t="n">
@@ -618,7 +722,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>26177</v>
       </c>
       <c r="B10" s="1" t="n">
@@ -651,7 +755,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>26207</v>
       </c>
       <c r="B11" s="1" t="n">
@@ -684,7 +788,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>26238</v>
       </c>
       <c r="B12" s="1" t="n">
@@ -717,7 +821,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>26268</v>
       </c>
       <c r="B13" s="1" t="n">
@@ -750,7 +854,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>26299</v>
       </c>
       <c r="B14" s="1" t="n">
@@ -783,7 +887,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>26330</v>
       </c>
       <c r="B15" s="1" t="n">
@@ -816,7 +920,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="5" t="n">
         <v>26359</v>
       </c>
       <c r="B16" s="1" t="n">
@@ -849,7 +953,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>26390</v>
       </c>
       <c r="B17" s="1" t="n">
@@ -882,7 +986,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="5" t="n">
         <v>26420</v>
       </c>
       <c r="B18" s="1" t="n">
@@ -915,7 +1019,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>26451</v>
       </c>
       <c r="B19" s="1" t="n">
@@ -948,7 +1052,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="5" t="n">
         <v>26481</v>
       </c>
       <c r="B20" s="1" t="n">
@@ -981,7 +1085,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="5" t="n">
         <v>26512</v>
       </c>
       <c r="B21" s="1" t="n">
@@ -1014,7 +1118,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="5" t="n">
         <v>26543</v>
       </c>
       <c r="B22" s="1" t="n">
@@ -1047,7 +1151,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="5" t="n">
         <v>26573</v>
       </c>
       <c r="B23" s="1" t="n">
@@ -1080,7 +1184,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="5" t="n">
         <v>26604</v>
       </c>
       <c r="B24" s="1" t="n">
@@ -1113,7 +1217,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="5" t="n">
         <v>26634</v>
       </c>
       <c r="B25" s="1" t="n">
@@ -1146,7 +1250,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="5" t="n">
         <v>26665</v>
       </c>
       <c r="B26" s="1" t="n">
@@ -1179,7 +1283,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="5" t="n">
         <v>26696</v>
       </c>
       <c r="B27" s="1" t="n">
@@ -1212,7 +1316,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="5" t="n">
         <v>26724</v>
       </c>
       <c r="B28" s="1" t="n">
@@ -1245,7 +1349,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="5" t="n">
         <v>26755</v>
       </c>
       <c r="B29" s="1" t="n">
@@ -1278,7 +1382,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="5" t="n">
         <v>26785</v>
       </c>
       <c r="B30" s="1" t="n">
@@ -1311,7 +1415,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="5" t="n">
         <v>26816</v>
       </c>
       <c r="B31" s="1" t="n">
@@ -1344,7 +1448,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="5" t="n">
         <v>26846</v>
       </c>
       <c r="B32" s="1" t="n">
@@ -1377,7 +1481,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="5" t="n">
         <v>26877</v>
       </c>
       <c r="B33" s="1" t="n">
@@ -1410,7 +1514,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="5" t="n">
         <v>26908</v>
       </c>
       <c r="B34" s="1" t="n">
@@ -1443,7 +1547,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="5" t="n">
         <v>26938</v>
       </c>
       <c r="B35" s="1" t="n">
@@ -1476,7 +1580,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="5" t="n">
         <v>26969</v>
       </c>
       <c r="B36" s="1" t="n">
@@ -1509,7 +1613,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="5" t="n">
         <v>26999</v>
       </c>
       <c r="B37" s="1" t="n">
@@ -1542,7 +1646,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="5" t="n">
         <v>27030</v>
       </c>
       <c r="B38" s="1" t="n">
@@ -1575,7 +1679,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="5" t="n">
         <v>27061</v>
       </c>
       <c r="B39" s="1" t="n">
@@ -1608,7 +1712,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="5" t="n">
         <v>27089</v>
       </c>
       <c r="B40" s="1" t="n">
@@ -1641,7 +1745,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="5" t="n">
         <v>27120</v>
       </c>
       <c r="B41" s="1" t="n">
@@ -1674,7 +1778,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="5" t="n">
         <v>27150</v>
       </c>
       <c r="B42" s="1" t="n">
@@ -1707,7 +1811,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="5" t="n">
         <v>27181</v>
       </c>
       <c r="B43" s="1" t="n">
@@ -1740,7 +1844,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="5" t="n">
         <v>27211</v>
       </c>
       <c r="B44" s="1" t="n">
@@ -1773,7 +1877,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="5" t="n">
         <v>27242</v>
       </c>
       <c r="B45" s="1" t="n">
@@ -1806,7 +1910,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="5" t="n">
         <v>27273</v>
       </c>
       <c r="B46" s="1" t="n">
@@ -1839,7 +1943,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="5" t="n">
         <v>27303</v>
       </c>
       <c r="B47" s="1" t="n">
@@ -1872,7 +1976,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="5" t="n">
         <v>27334</v>
       </c>
       <c r="B48" s="1" t="n">
@@ -1905,7 +2009,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="5" t="n">
         <v>27364</v>
       </c>
       <c r="B49" s="1" t="n">
@@ -1938,7 +2042,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="5" t="n">
         <v>27395</v>
       </c>
       <c r="B50" s="1" t="n">
@@ -1971,7 +2075,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="5" t="n">
         <v>27426</v>
       </c>
       <c r="B51" s="1" t="n">
@@ -2004,7 +2108,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="5" t="n">
         <v>27454</v>
       </c>
       <c r="B52" s="1" t="n">
@@ -2037,7 +2141,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="5" t="n">
         <v>27485</v>
       </c>
       <c r="B53" s="1" t="n">
@@ -2070,7 +2174,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="5" t="n">
         <v>27515</v>
       </c>
       <c r="B54" s="1" t="n">
@@ -2103,7 +2207,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="5" t="n">
         <v>27546</v>
       </c>
       <c r="B55" s="1" t="n">
@@ -2136,7 +2240,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="5" t="n">
         <v>27576</v>
       </c>
       <c r="B56" s="1" t="n">
@@ -2169,7 +2273,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="5" t="n">
         <v>27607</v>
       </c>
       <c r="B57" s="1" t="n">
@@ -2202,7 +2306,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="5" t="n">
         <v>27638</v>
       </c>
       <c r="B58" s="1" t="n">
@@ -2235,7 +2339,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="5" t="n">
         <v>27668</v>
       </c>
       <c r="B59" s="1" t="n">
@@ -2268,7 +2372,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="5" t="n">
         <v>27699</v>
       </c>
       <c r="B60" s="1" t="n">
@@ -2301,7 +2405,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="5" t="n">
         <v>27729</v>
       </c>
       <c r="B61" s="1" t="n">
@@ -2334,7 +2438,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="5" t="n">
         <v>27760</v>
       </c>
       <c r="B62" s="1" t="n">
@@ -2367,7 +2471,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="5" t="n">
         <v>27791</v>
       </c>
       <c r="B63" s="1" t="n">
@@ -2400,7 +2504,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="5" t="n">
         <v>27820</v>
       </c>
       <c r="B64" s="1" t="n">
@@ -2433,7 +2537,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="5" t="n">
         <v>27851</v>
       </c>
       <c r="B65" s="1" t="n">
@@ -2466,7 +2570,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="5" t="n">
         <v>27881</v>
       </c>
       <c r="B66" s="1" t="n">
@@ -2499,7 +2603,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="5" t="n">
         <v>27912</v>
       </c>
       <c r="B67" s="1" t="n">
@@ -2532,7 +2636,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="5" t="n">
         <v>27942</v>
       </c>
       <c r="B68" s="1" t="n">
@@ -2565,7 +2669,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="5" t="n">
         <v>27973</v>
       </c>
       <c r="B69" s="1" t="n">
@@ -2598,7 +2702,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="5" t="n">
         <v>28004</v>
       </c>
       <c r="B70" s="1" t="n">
@@ -2631,7 +2735,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="5" t="n">
         <v>28034</v>
       </c>
       <c r="B71" s="1" t="n">
@@ -2664,7 +2768,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="5" t="n">
         <v>28065</v>
       </c>
       <c r="B72" s="1" t="n">
@@ -2697,7 +2801,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="5" t="n">
         <v>28095</v>
       </c>
       <c r="B73" s="1" t="n">
@@ -2730,7 +2834,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="5" t="n">
         <v>28126</v>
       </c>
       <c r="B74" s="1" t="n">
@@ -2763,7 +2867,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="5" t="n">
         <v>28157</v>
       </c>
       <c r="B75" s="1" t="n">
@@ -2796,7 +2900,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="5" t="n">
         <v>28185</v>
       </c>
       <c r="B76" s="1" t="n">
@@ -2829,7 +2933,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="5" t="n">
         <v>28216</v>
       </c>
       <c r="B77" s="1" t="n">
@@ -2862,7 +2966,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="5" t="n">
         <v>28246</v>
       </c>
       <c r="B78" s="1" t="n">
@@ -2895,7 +2999,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="5" t="n">
         <v>28277</v>
       </c>
       <c r="B79" s="1" t="n">
@@ -2928,7 +3032,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
+      <c r="A80" s="5" t="n">
         <v>28307</v>
       </c>
       <c r="B80" s="1" t="n">
@@ -2961,7 +3065,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="5" t="n">
         <v>28338</v>
       </c>
       <c r="B81" s="1" t="n">
@@ -2994,7 +3098,7 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="5" t="n">
         <v>28369</v>
       </c>
       <c r="B82" s="1" t="n">
@@ -3027,7 +3131,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="5" t="n">
         <v>28399</v>
       </c>
       <c r="B83" s="1" t="n">
@@ -3060,7 +3164,7 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="n">
+      <c r="A84" s="5" t="n">
         <v>28430</v>
       </c>
       <c r="B84" s="1" t="n">
@@ -3093,7 +3197,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="5" t="n">
         <v>28460</v>
       </c>
       <c r="B85" s="1" t="n">
@@ -3126,7 +3230,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="5" t="n">
         <v>28491</v>
       </c>
       <c r="B86" s="1" t="n">
@@ -3159,7 +3263,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="5" t="n">
         <v>28522</v>
       </c>
       <c r="B87" s="1" t="n">
@@ -3192,7 +3296,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="5" t="n">
         <v>28550</v>
       </c>
       <c r="B88" s="1" t="n">
@@ -3225,7 +3329,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="5" t="n">
         <v>28581</v>
       </c>
       <c r="B89" s="1" t="n">
@@ -3258,7 +3362,7 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="n">
+      <c r="A90" s="5" t="n">
         <v>28611</v>
       </c>
       <c r="B90" s="1" t="n">
@@ -3291,7 +3395,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="5" t="n">
         <v>28642</v>
       </c>
       <c r="B91" s="1" t="n">
@@ -3324,7 +3428,7 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="n">
+      <c r="A92" s="5" t="n">
         <v>28672</v>
       </c>
       <c r="B92" s="1" t="n">
@@ -3357,7 +3461,7 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="5" t="n">
         <v>28703</v>
       </c>
       <c r="B93" s="1" t="n">
@@ -3390,7 +3494,7 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="5" t="n">
         <v>28734</v>
       </c>
       <c r="B94" s="1" t="n">
@@ -3423,7 +3527,7 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="5" t="n">
         <v>28764</v>
       </c>
       <c r="B95" s="1" t="n">
@@ -3456,7 +3560,7 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
+      <c r="A96" s="5" t="n">
         <v>28795</v>
       </c>
       <c r="B96" s="1" t="n">
@@ -3489,7 +3593,7 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="5" t="n">
         <v>28825</v>
       </c>
       <c r="B97" s="1" t="n">
@@ -3522,7 +3626,7 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="n">
+      <c r="A98" s="5" t="n">
         <v>28856</v>
       </c>
       <c r="B98" s="1" t="n">
@@ -3555,7 +3659,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="n">
+      <c r="A99" s="5" t="n">
         <v>28887</v>
       </c>
       <c r="B99" s="1" t="n">
@@ -3588,7 +3692,7 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="n">
+      <c r="A100" s="5" t="n">
         <v>28915</v>
       </c>
       <c r="B100" s="1" t="n">
@@ -3621,7 +3725,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="n">
+      <c r="A101" s="5" t="n">
         <v>28946</v>
       </c>
       <c r="B101" s="1" t="n">
@@ -3654,7 +3758,7 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="n">
+      <c r="A102" s="5" t="n">
         <v>28976</v>
       </c>
       <c r="B102" s="1" t="n">
@@ -3687,7 +3791,7 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4" t="n">
+      <c r="A103" s="5" t="n">
         <v>29007</v>
       </c>
       <c r="B103" s="1" t="n">
@@ -3720,7 +3824,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4" t="n">
+      <c r="A104" s="5" t="n">
         <v>29037</v>
       </c>
       <c r="B104" s="1" t="n">
@@ -3753,7 +3857,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4" t="n">
+      <c r="A105" s="5" t="n">
         <v>29068</v>
       </c>
       <c r="B105" s="1" t="n">
@@ -3786,7 +3890,7 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="4" t="n">
+      <c r="A106" s="5" t="n">
         <v>29099</v>
       </c>
       <c r="B106" s="1" t="n">
@@ -3819,7 +3923,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="4" t="n">
+      <c r="A107" s="5" t="n">
         <v>29129</v>
       </c>
       <c r="B107" s="1" t="n">
@@ -3852,7 +3956,7 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="n">
+      <c r="A108" s="5" t="n">
         <v>29160</v>
       </c>
       <c r="B108" s="1" t="n">
@@ -3885,7 +3989,7 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="n">
+      <c r="A109" s="5" t="n">
         <v>29190</v>
       </c>
       <c r="B109" s="1" t="n">
@@ -3918,7 +4022,7 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="n">
+      <c r="A110" s="5" t="n">
         <v>29221</v>
       </c>
       <c r="B110" s="1" t="n">
@@ -3951,7 +4055,7 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="4" t="n">
+      <c r="A111" s="5" t="n">
         <v>29252</v>
       </c>
       <c r="B111" s="1" t="n">
@@ -3984,7 +4088,7 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="4" t="n">
+      <c r="A112" s="5" t="n">
         <v>29281</v>
       </c>
       <c r="B112" s="1" t="n">
@@ -4017,7 +4121,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="4" t="n">
+      <c r="A113" s="5" t="n">
         <v>29312</v>
       </c>
       <c r="B113" s="1" t="n">
@@ -4050,7 +4154,7 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="4" t="n">
+      <c r="A114" s="5" t="n">
         <v>29342</v>
       </c>
       <c r="B114" s="1" t="n">
@@ -4083,7 +4187,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="4" t="n">
+      <c r="A115" s="5" t="n">
         <v>29373</v>
       </c>
       <c r="B115" s="1" t="n">
@@ -4116,7 +4220,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="4" t="n">
+      <c r="A116" s="5" t="n">
         <v>29403</v>
       </c>
       <c r="B116" s="1" t="n">
@@ -4149,7 +4253,7 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="n">
+      <c r="A117" s="5" t="n">
         <v>29434</v>
       </c>
       <c r="B117" s="1" t="n">
@@ -4182,7 +4286,7 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="n">
+      <c r="A118" s="5" t="n">
         <v>29465</v>
       </c>
       <c r="B118" s="1" t="n">
@@ -4215,7 +4319,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="4" t="n">
+      <c r="A119" s="5" t="n">
         <v>29495</v>
       </c>
       <c r="B119" s="1" t="n">
@@ -4248,7 +4352,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4" t="n">
+      <c r="A120" s="5" t="n">
         <v>29526</v>
       </c>
       <c r="B120" s="1" t="n">
@@ -4281,7 +4385,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="4" t="n">
+      <c r="A121" s="5" t="n">
         <v>29556</v>
       </c>
       <c r="B121" s="1" t="n">
@@ -4314,7 +4418,7 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="4" t="n">
+      <c r="A122" s="5" t="n">
         <v>29587</v>
       </c>
       <c r="B122" s="1" t="n">
@@ -4347,7 +4451,7 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="4" t="n">
+      <c r="A123" s="5" t="n">
         <v>29618</v>
       </c>
       <c r="B123" s="1" t="n">
@@ -4380,7 +4484,7 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="4" t="n">
+      <c r="A124" s="5" t="n">
         <v>29646</v>
       </c>
       <c r="B124" s="1" t="n">
@@ -4413,7 +4517,7 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="4" t="n">
+      <c r="A125" s="5" t="n">
         <v>29677</v>
       </c>
       <c r="B125" s="1" t="n">
@@ -4446,7 +4550,7 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="4" t="n">
+      <c r="A126" s="5" t="n">
         <v>29707</v>
       </c>
       <c r="B126" s="1" t="n">
@@ -4479,7 +4583,7 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="4" t="n">
+      <c r="A127" s="5" t="n">
         <v>29738</v>
       </c>
       <c r="B127" s="1" t="n">
@@ -4512,7 +4616,7 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="4" t="n">
+      <c r="A128" s="5" t="n">
         <v>29768</v>
       </c>
       <c r="B128" s="1" t="n">
@@ -4545,7 +4649,7 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="4" t="n">
+      <c r="A129" s="5" t="n">
         <v>29799</v>
       </c>
       <c r="B129" s="1" t="n">
@@ -4578,7 +4682,7 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="4" t="n">
+      <c r="A130" s="5" t="n">
         <v>29830</v>
       </c>
       <c r="B130" s="1" t="n">
@@ -4611,7 +4715,7 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="4" t="n">
+      <c r="A131" s="5" t="n">
         <v>29860</v>
       </c>
       <c r="B131" s="1" t="n">
@@ -4644,7 +4748,7 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="4" t="n">
+      <c r="A132" s="5" t="n">
         <v>29891</v>
       </c>
       <c r="B132" s="1" t="n">
@@ -4677,7 +4781,7 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="4" t="n">
+      <c r="A133" s="5" t="n">
         <v>29921</v>
       </c>
       <c r="B133" s="1" t="n">
@@ -4710,7 +4814,7 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="4" t="n">
+      <c r="A134" s="5" t="n">
         <v>29952</v>
       </c>
       <c r="B134" s="1" t="n">
@@ -4743,7 +4847,7 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="4" t="n">
+      <c r="A135" s="5" t="n">
         <v>29983</v>
       </c>
       <c r="B135" s="1" t="n">
@@ -4776,7 +4880,7 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="4" t="n">
+      <c r="A136" s="5" t="n">
         <v>30011</v>
       </c>
       <c r="B136" s="1" t="n">
@@ -4809,7 +4913,7 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="4" t="n">
+      <c r="A137" s="5" t="n">
         <v>30042</v>
       </c>
       <c r="B137" s="1" t="n">
@@ -4842,7 +4946,7 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="4" t="n">
+      <c r="A138" s="5" t="n">
         <v>30072</v>
       </c>
       <c r="B138" s="1" t="n">
@@ -4875,7 +4979,7 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="4" t="n">
+      <c r="A139" s="5" t="n">
         <v>30103</v>
       </c>
       <c r="B139" s="1" t="n">
@@ -4908,7 +5012,7 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="4" t="n">
+      <c r="A140" s="5" t="n">
         <v>30133</v>
       </c>
       <c r="B140" s="1" t="n">
@@ -4941,7 +5045,7 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="4" t="n">
+      <c r="A141" s="5" t="n">
         <v>30164</v>
       </c>
       <c r="B141" s="1" t="n">
@@ -4974,7 +5078,7 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="4" t="n">
+      <c r="A142" s="5" t="n">
         <v>30195</v>
       </c>
       <c r="B142" s="1" t="n">
@@ -5007,7 +5111,7 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="4" t="n">
+      <c r="A143" s="5" t="n">
         <v>30225</v>
       </c>
       <c r="B143" s="1" t="n">
@@ -5040,7 +5144,7 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="4" t="n">
+      <c r="A144" s="5" t="n">
         <v>30256</v>
       </c>
       <c r="B144" s="1" t="n">
@@ -5073,7 +5177,7 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="4" t="n">
+      <c r="A145" s="5" t="n">
         <v>30286</v>
       </c>
       <c r="B145" s="1" t="n">
@@ -5106,7 +5210,7 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="4" t="n">
+      <c r="A146" s="5" t="n">
         <v>30317</v>
       </c>
       <c r="B146" s="1" t="n">
@@ -5139,7 +5243,7 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="4" t="n">
+      <c r="A147" s="5" t="n">
         <v>30348</v>
       </c>
       <c r="B147" s="1" t="n">
@@ -5172,7 +5276,7 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="4" t="n">
+      <c r="A148" s="5" t="n">
         <v>30376</v>
       </c>
       <c r="B148" s="1" t="n">
@@ -5205,7 +5309,7 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="4" t="n">
+      <c r="A149" s="5" t="n">
         <v>30407</v>
       </c>
       <c r="B149" s="1" t="n">
@@ -5238,7 +5342,7 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="4" t="n">
+      <c r="A150" s="5" t="n">
         <v>30437</v>
       </c>
       <c r="B150" s="1" t="n">
@@ -5271,7 +5375,7 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="4" t="n">
+      <c r="A151" s="5" t="n">
         <v>30468</v>
       </c>
       <c r="B151" s="1" t="n">
@@ -5304,7 +5408,7 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="4" t="n">
+      <c r="A152" s="5" t="n">
         <v>30498</v>
       </c>
       <c r="B152" s="1" t="n">
@@ -5337,7 +5441,7 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="4" t="n">
+      <c r="A153" s="5" t="n">
         <v>30529</v>
       </c>
       <c r="B153" s="1" t="n">
@@ -5370,7 +5474,7 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="4" t="n">
+      <c r="A154" s="5" t="n">
         <v>30560</v>
       </c>
       <c r="B154" s="1" t="n">
@@ -5403,7 +5507,7 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="4" t="n">
+      <c r="A155" s="5" t="n">
         <v>30590</v>
       </c>
       <c r="B155" s="1" t="n">
@@ -5436,7 +5540,7 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="4" t="n">
+      <c r="A156" s="5" t="n">
         <v>30621</v>
       </c>
       <c r="B156" s="1" t="n">
@@ -5469,7 +5573,7 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="4" t="n">
+      <c r="A157" s="5" t="n">
         <v>30651</v>
       </c>
       <c r="B157" s="1" t="n">
@@ -5502,7 +5606,7 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="4" t="n">
+      <c r="A158" s="5" t="n">
         <v>30682</v>
       </c>
       <c r="B158" s="1" t="n">
@@ -5535,7 +5639,7 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="4" t="n">
+      <c r="A159" s="5" t="n">
         <v>30713</v>
       </c>
       <c r="B159" s="1" t="n">
@@ -5568,7 +5672,7 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="4" t="n">
+      <c r="A160" s="5" t="n">
         <v>30742</v>
       </c>
       <c r="B160" s="1" t="n">
@@ -5601,7 +5705,7 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="4" t="n">
+      <c r="A161" s="5" t="n">
         <v>30773</v>
       </c>
       <c r="B161" s="1" t="n">
@@ -5634,7 +5738,7 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="4" t="n">
+      <c r="A162" s="5" t="n">
         <v>30803</v>
       </c>
       <c r="B162" s="1" t="n">
@@ -5667,7 +5771,7 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="4" t="n">
+      <c r="A163" s="5" t="n">
         <v>30834</v>
       </c>
       <c r="B163" s="1" t="n">
@@ -5700,7 +5804,7 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="4" t="n">
+      <c r="A164" s="5" t="n">
         <v>30864</v>
       </c>
       <c r="B164" s="1" t="n">
@@ -5733,7 +5837,7 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="4" t="n">
+      <c r="A165" s="5" t="n">
         <v>30895</v>
       </c>
       <c r="B165" s="1" t="n">
@@ -5766,7 +5870,7 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="4" t="n">
+      <c r="A166" s="5" t="n">
         <v>30926</v>
       </c>
       <c r="B166" s="1" t="n">
@@ -5799,7 +5903,7 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="4" t="n">
+      <c r="A167" s="5" t="n">
         <v>30956</v>
       </c>
       <c r="B167" s="1" t="n">
@@ -5832,7 +5936,7 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="4" t="n">
+      <c r="A168" s="5" t="n">
         <v>30987</v>
       </c>
       <c r="B168" s="1" t="n">
@@ -5865,7 +5969,7 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="4" t="n">
+      <c r="A169" s="5" t="n">
         <v>31017</v>
       </c>
       <c r="B169" s="1" t="n">
@@ -5898,7 +6002,7 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="4" t="n">
+      <c r="A170" s="5" t="n">
         <v>31048</v>
       </c>
       <c r="B170" s="1" t="n">
@@ -5931,7 +6035,7 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="4" t="n">
+      <c r="A171" s="5" t="n">
         <v>31079</v>
       </c>
       <c r="B171" s="1" t="n">
@@ -5964,7 +6068,7 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="4" t="n">
+      <c r="A172" s="5" t="n">
         <v>31107</v>
       </c>
       <c r="B172" s="1" t="n">
@@ -5997,7 +6101,7 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="4" t="n">
+      <c r="A173" s="5" t="n">
         <v>31138</v>
       </c>
       <c r="B173" s="1" t="n">
@@ -6030,7 +6134,7 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="4" t="n">
+      <c r="A174" s="5" t="n">
         <v>31168</v>
       </c>
       <c r="B174" s="1" t="n">
@@ -6063,7 +6167,7 @@
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="4" t="n">
+      <c r="A175" s="5" t="n">
         <v>31199</v>
       </c>
       <c r="B175" s="1" t="n">
@@ -6096,7 +6200,7 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="4" t="n">
+      <c r="A176" s="5" t="n">
         <v>31229</v>
       </c>
       <c r="B176" s="1" t="n">
@@ -6129,7 +6233,7 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="4" t="n">
+      <c r="A177" s="5" t="n">
         <v>31260</v>
       </c>
       <c r="B177" s="1" t="n">
@@ -6162,7 +6266,7 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="4" t="n">
+      <c r="A178" s="5" t="n">
         <v>31291</v>
       </c>
       <c r="B178" s="1" t="n">
@@ -6195,7 +6299,7 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="4" t="n">
+      <c r="A179" s="5" t="n">
         <v>31321</v>
       </c>
       <c r="B179" s="1" t="n">
@@ -6228,7 +6332,7 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="4" t="n">
+      <c r="A180" s="5" t="n">
         <v>31352</v>
       </c>
       <c r="B180" s="1" t="n">
@@ -6261,7 +6365,7 @@
       </c>
     </row>
     <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="4" t="n">
+      <c r="A181" s="5" t="n">
         <v>31382</v>
       </c>
       <c r="B181" s="1" t="n">
@@ -6294,7 +6398,7 @@
       </c>
     </row>
     <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="4" t="n">
+      <c r="A182" s="5" t="n">
         <v>31413</v>
       </c>
       <c r="B182" s="1" t="n">
@@ -6327,7 +6431,7 @@
       </c>
     </row>
     <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="4" t="n">
+      <c r="A183" s="5" t="n">
         <v>31444</v>
       </c>
       <c r="B183" s="1" t="n">
@@ -6360,7 +6464,7 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="4" t="n">
+      <c r="A184" s="5" t="n">
         <v>31472</v>
       </c>
       <c r="B184" s="1" t="n">
@@ -6393,7 +6497,7 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="4" t="n">
+      <c r="A185" s="5" t="n">
         <v>31503</v>
       </c>
       <c r="B185" s="1" t="n">
@@ -6426,7 +6530,7 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="4" t="n">
+      <c r="A186" s="5" t="n">
         <v>31533</v>
       </c>
       <c r="B186" s="1" t="n">
@@ -6459,7 +6563,7 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="4" t="n">
+      <c r="A187" s="5" t="n">
         <v>31564</v>
       </c>
       <c r="B187" s="1" t="n">
@@ -6492,7 +6596,7 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="4" t="n">
+      <c r="A188" s="5" t="n">
         <v>31594</v>
       </c>
       <c r="B188" s="1" t="n">
@@ -6525,7 +6629,7 @@
       </c>
     </row>
     <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="4" t="n">
+      <c r="A189" s="5" t="n">
         <v>31625</v>
       </c>
       <c r="B189" s="1" t="n">
@@ -6558,7 +6662,7 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="4" t="n">
+      <c r="A190" s="5" t="n">
         <v>31656</v>
       </c>
       <c r="B190" s="1" t="n">
@@ -6591,7 +6695,7 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="4" t="n">
+      <c r="A191" s="5" t="n">
         <v>31686</v>
       </c>
       <c r="B191" s="1" t="n">
@@ -6624,7 +6728,7 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="4" t="n">
+      <c r="A192" s="5" t="n">
         <v>31717</v>
       </c>
       <c r="B192" s="1" t="n">
@@ -6657,7 +6761,7 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="4" t="n">
+      <c r="A193" s="5" t="n">
         <v>31747</v>
       </c>
       <c r="B193" s="1" t="n">
@@ -6690,7 +6794,7 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="4" t="n">
+      <c r="A194" s="5" t="n">
         <v>31778</v>
       </c>
       <c r="B194" s="1" t="n">
@@ -6723,7 +6827,7 @@
       </c>
     </row>
     <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="4" t="n">
+      <c r="A195" s="5" t="n">
         <v>31809</v>
       </c>
       <c r="B195" s="1" t="n">
@@ -6756,7 +6860,7 @@
       </c>
     </row>
     <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="4" t="n">
+      <c r="A196" s="5" t="n">
         <v>31837</v>
       </c>
       <c r="B196" s="1" t="n">
@@ -6789,7 +6893,7 @@
       </c>
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="4" t="n">
+      <c r="A197" s="5" t="n">
         <v>31868</v>
       </c>
       <c r="B197" s="1" t="n">
@@ -6822,7 +6926,7 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="4" t="n">
+      <c r="A198" s="5" t="n">
         <v>31898</v>
       </c>
       <c r="B198" s="1" t="n">
@@ -6855,7 +6959,7 @@
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="4" t="n">
+      <c r="A199" s="5" t="n">
         <v>31929</v>
       </c>
       <c r="B199" s="1" t="n">
@@ -6888,7 +6992,7 @@
       </c>
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="4" t="n">
+      <c r="A200" s="5" t="n">
         <v>31959</v>
       </c>
       <c r="B200" s="1" t="n">
@@ -6921,7 +7025,7 @@
       </c>
     </row>
     <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="4" t="n">
+      <c r="A201" s="5" t="n">
         <v>31990</v>
       </c>
       <c r="B201" s="1" t="n">
@@ -6954,7 +7058,7 @@
       </c>
     </row>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="4" t="n">
+      <c r="A202" s="5" t="n">
         <v>32021</v>
       </c>
       <c r="B202" s="1" t="n">
@@ -6987,7 +7091,7 @@
       </c>
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="4" t="n">
+      <c r="A203" s="5" t="n">
         <v>32051</v>
       </c>
       <c r="B203" s="1" t="n">
@@ -7020,7 +7124,7 @@
       </c>
     </row>
     <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="4" t="n">
+      <c r="A204" s="5" t="n">
         <v>32082</v>
       </c>
       <c r="B204" s="1" t="n">
@@ -7053,7 +7157,7 @@
       </c>
     </row>
     <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="4" t="n">
+      <c r="A205" s="5" t="n">
         <v>32112</v>
       </c>
       <c r="B205" s="1" t="n">
@@ -7086,7 +7190,7 @@
       </c>
     </row>
     <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="4" t="n">
+      <c r="A206" s="5" t="n">
         <v>32143</v>
       </c>
       <c r="B206" s="1" t="n">
@@ -7119,7 +7223,7 @@
       </c>
     </row>
     <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="4" t="n">
+      <c r="A207" s="5" t="n">
         <v>32174</v>
       </c>
       <c r="B207" s="1" t="n">
@@ -7152,7 +7256,7 @@
       </c>
     </row>
     <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="4" t="n">
+      <c r="A208" s="5" t="n">
         <v>32203</v>
       </c>
       <c r="B208" s="1" t="n">
@@ -7185,7 +7289,7 @@
       </c>
     </row>
     <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="4" t="n">
+      <c r="A209" s="5" t="n">
         <v>32234</v>
       </c>
       <c r="B209" s="1" t="n">
@@ -7218,7 +7322,7 @@
       </c>
     </row>
     <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="4" t="n">
+      <c r="A210" s="5" t="n">
         <v>32264</v>
       </c>
       <c r="B210" s="1" t="n">
@@ -7251,7 +7355,7 @@
       </c>
     </row>
     <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="4" t="n">
+      <c r="A211" s="5" t="n">
         <v>32295</v>
       </c>
       <c r="B211" s="1" t="n">
@@ -7284,7 +7388,7 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="4" t="n">
+      <c r="A212" s="5" t="n">
         <v>32325</v>
       </c>
       <c r="B212" s="1" t="n">
@@ -7317,7 +7421,7 @@
       </c>
     </row>
     <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="4" t="n">
+      <c r="A213" s="5" t="n">
         <v>32356</v>
       </c>
       <c r="B213" s="1" t="n">
@@ -7350,7 +7454,7 @@
       </c>
     </row>
     <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="4" t="n">
+      <c r="A214" s="5" t="n">
         <v>32387</v>
       </c>
       <c r="B214" s="1" t="n">
@@ -7383,7 +7487,7 @@
       </c>
     </row>
     <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="4" t="n">
+      <c r="A215" s="5" t="n">
         <v>32417</v>
       </c>
       <c r="B215" s="1" t="n">
@@ -7416,7 +7520,7 @@
       </c>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="4" t="n">
+      <c r="A216" s="5" t="n">
         <v>32448</v>
       </c>
       <c r="B216" s="1" t="n">
@@ -7449,7 +7553,7 @@
       </c>
     </row>
     <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="4" t="n">
+      <c r="A217" s="5" t="n">
         <v>32478</v>
       </c>
       <c r="B217" s="1" t="n">
@@ -7482,7 +7586,7 @@
       </c>
     </row>
     <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="4" t="n">
+      <c r="A218" s="5" t="n">
         <v>32509</v>
       </c>
       <c r="B218" s="1" t="n">
@@ -7515,7 +7619,7 @@
       </c>
     </row>
     <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="4" t="n">
+      <c r="A219" s="5" t="n">
         <v>32540</v>
       </c>
       <c r="B219" s="1" t="n">
@@ -7548,7 +7652,7 @@
       </c>
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="4" t="n">
+      <c r="A220" s="5" t="n">
         <v>32568</v>
       </c>
       <c r="B220" s="1" t="n">
@@ -7581,7 +7685,7 @@
       </c>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="4" t="n">
+      <c r="A221" s="5" t="n">
         <v>32599</v>
       </c>
       <c r="B221" s="1" t="n">
@@ -7614,7 +7718,7 @@
       </c>
     </row>
     <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="4" t="n">
+      <c r="A222" s="5" t="n">
         <v>32629</v>
       </c>
       <c r="B222" s="1" t="n">
@@ -7647,7 +7751,7 @@
       </c>
     </row>
     <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="4" t="n">
+      <c r="A223" s="5" t="n">
         <v>32660</v>
       </c>
       <c r="B223" s="1" t="n">
@@ -7680,7 +7784,7 @@
       </c>
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="4" t="n">
+      <c r="A224" s="5" t="n">
         <v>32690</v>
       </c>
       <c r="B224" s="1" t="n">
@@ -7713,7 +7817,7 @@
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="4" t="n">
+      <c r="A225" s="5" t="n">
         <v>32721</v>
       </c>
       <c r="B225" s="1" t="n">
@@ -7746,7 +7850,7 @@
       </c>
     </row>
     <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="4" t="n">
+      <c r="A226" s="5" t="n">
         <v>32752</v>
       </c>
       <c r="B226" s="1" t="n">
@@ -7779,7 +7883,7 @@
       </c>
     </row>
     <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="4" t="n">
+      <c r="A227" s="5" t="n">
         <v>32782</v>
       </c>
       <c r="B227" s="1" t="n">
@@ -7812,7 +7916,7 @@
       </c>
     </row>
     <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="4" t="n">
+      <c r="A228" s="5" t="n">
         <v>32813</v>
       </c>
       <c r="B228" s="1" t="n">
@@ -7845,7 +7949,7 @@
       </c>
     </row>
     <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="4" t="n">
+      <c r="A229" s="5" t="n">
         <v>32843</v>
       </c>
       <c r="B229" s="1" t="n">
@@ -7878,7 +7982,7 @@
       </c>
     </row>
     <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="4" t="n">
+      <c r="A230" s="5" t="n">
         <v>32874</v>
       </c>
       <c r="B230" s="1" t="n">
@@ -7911,7 +8015,7 @@
       </c>
     </row>
     <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="4" t="n">
+      <c r="A231" s="5" t="n">
         <v>32905</v>
       </c>
       <c r="B231" s="1" t="n">
@@ -7944,7 +8048,7 @@
       </c>
     </row>
     <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="4" t="n">
+      <c r="A232" s="5" t="n">
         <v>32933</v>
       </c>
       <c r="B232" s="1" t="n">
@@ -7977,7 +8081,7 @@
       </c>
     </row>
     <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="4" t="n">
+      <c r="A233" s="5" t="n">
         <v>32964</v>
       </c>
       <c r="B233" s="1" t="n">
@@ -8010,7 +8114,7 @@
       </c>
     </row>
     <row r="234" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="4" t="n">
+      <c r="A234" s="5" t="n">
         <v>32994</v>
       </c>
       <c r="B234" s="1" t="n">
@@ -8043,7 +8147,7 @@
       </c>
     </row>
     <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="4" t="n">
+      <c r="A235" s="5" t="n">
         <v>33025</v>
       </c>
       <c r="B235" s="1" t="n">
@@ -8076,7 +8180,7 @@
       </c>
     </row>
     <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="4" t="n">
+      <c r="A236" s="5" t="n">
         <v>33055</v>
       </c>
       <c r="B236" s="1" t="n">
@@ -8109,7 +8213,7 @@
       </c>
     </row>
     <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="4" t="n">
+      <c r="A237" s="5" t="n">
         <v>33086</v>
       </c>
       <c r="B237" s="1" t="n">
@@ -8142,7 +8246,7 @@
       </c>
     </row>
     <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="4" t="n">
+      <c r="A238" s="5" t="n">
         <v>33117</v>
       </c>
       <c r="B238" s="1" t="n">
@@ -8175,7 +8279,7 @@
       </c>
     </row>
     <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="4" t="n">
+      <c r="A239" s="5" t="n">
         <v>33147</v>
       </c>
       <c r="B239" s="1" t="n">
@@ -8208,7 +8312,7 @@
       </c>
     </row>
     <row r="240" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="4" t="n">
+      <c r="A240" s="5" t="n">
         <v>33178</v>
       </c>
       <c r="B240" s="1" t="n">
@@ -8241,7 +8345,7 @@
       </c>
     </row>
     <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="4" t="n">
+      <c r="A241" s="5" t="n">
         <v>33208</v>
       </c>
       <c r="B241" s="1" t="n">
@@ -8274,7 +8378,7 @@
       </c>
     </row>
     <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="4" t="n">
+      <c r="A242" s="5" t="n">
         <v>33239</v>
       </c>
       <c r="B242" s="1" t="n">
@@ -8307,7 +8411,7 @@
       </c>
     </row>
     <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="4" t="n">
+      <c r="A243" s="5" t="n">
         <v>33270</v>
       </c>
       <c r="B243" s="1" t="n">
@@ -8340,7 +8444,7 @@
       </c>
     </row>
     <row r="244" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="4" t="n">
+      <c r="A244" s="5" t="n">
         <v>33298</v>
       </c>
       <c r="B244" s="1" t="n">
@@ -8373,7 +8477,7 @@
       </c>
     </row>
     <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="4" t="n">
+      <c r="A245" s="5" t="n">
         <v>33329</v>
       </c>
       <c r="B245" s="1" t="n">
@@ -8406,7 +8510,7 @@
       </c>
     </row>
     <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="4" t="n">
+      <c r="A246" s="5" t="n">
         <v>33359</v>
       </c>
       <c r="B246" s="1" t="n">
@@ -8439,7 +8543,7 @@
       </c>
     </row>
     <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="4" t="n">
+      <c r="A247" s="5" t="n">
         <v>33390</v>
       </c>
       <c r="B247" s="1" t="n">
@@ -8472,7 +8576,7 @@
       </c>
     </row>
     <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="4" t="n">
+      <c r="A248" s="5" t="n">
         <v>33420</v>
       </c>
       <c r="B248" s="1" t="n">
@@ -8505,7 +8609,7 @@
       </c>
     </row>
     <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="4" t="n">
+      <c r="A249" s="5" t="n">
         <v>33451</v>
       </c>
       <c r="B249" s="1" t="n">
@@ -8538,7 +8642,7 @@
       </c>
     </row>
     <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="4" t="n">
+      <c r="A250" s="5" t="n">
         <v>33482</v>
       </c>
       <c r="B250" s="1" t="n">
@@ -8571,7 +8675,7 @@
       </c>
     </row>
     <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="4" t="n">
+      <c r="A251" s="5" t="n">
         <v>33512</v>
       </c>
       <c r="B251" s="1" t="n">
@@ -8604,7 +8708,7 @@
       </c>
     </row>
     <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="4" t="n">
+      <c r="A252" s="5" t="n">
         <v>33543</v>
       </c>
       <c r="B252" s="1" t="n">
@@ -8637,7 +8741,7 @@
       </c>
     </row>
     <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="4" t="n">
+      <c r="A253" s="5" t="n">
         <v>33573</v>
       </c>
       <c r="B253" s="1" t="n">
@@ -8670,7 +8774,7 @@
       </c>
     </row>
     <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="4" t="n">
+      <c r="A254" s="5" t="n">
         <v>33604</v>
       </c>
       <c r="B254" s="1" t="n">
@@ -8703,7 +8807,7 @@
       </c>
     </row>
     <row r="255" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="4" t="n">
+      <c r="A255" s="5" t="n">
         <v>33635</v>
       </c>
       <c r="B255" s="1" t="n">
@@ -8736,7 +8840,7 @@
       </c>
     </row>
     <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="4" t="n">
+      <c r="A256" s="5" t="n">
         <v>33664</v>
       </c>
       <c r="B256" s="1" t="n">
@@ -8769,7 +8873,7 @@
       </c>
     </row>
     <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="4" t="n">
+      <c r="A257" s="5" t="n">
         <v>33695</v>
       </c>
       <c r="B257" s="1" t="n">
@@ -8802,7 +8906,7 @@
       </c>
     </row>
     <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="4" t="n">
+      <c r="A258" s="5" t="n">
         <v>33725</v>
       </c>
       <c r="B258" s="1" t="n">
@@ -8835,7 +8939,7 @@
       </c>
     </row>
     <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="4" t="n">
+      <c r="A259" s="5" t="n">
         <v>33756</v>
       </c>
       <c r="B259" s="1" t="n">
@@ -8868,7 +8972,7 @@
       </c>
     </row>
     <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="4" t="n">
+      <c r="A260" s="5" t="n">
         <v>33786</v>
       </c>
       <c r="B260" s="1" t="n">
@@ -8901,7 +9005,7 @@
       </c>
     </row>
     <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="4" t="n">
+      <c r="A261" s="5" t="n">
         <v>33817</v>
       </c>
       <c r="B261" s="1" t="n">
@@ -8934,7 +9038,7 @@
       </c>
     </row>
     <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="4" t="n">
+      <c r="A262" s="5" t="n">
         <v>33848</v>
       </c>
       <c r="B262" s="1" t="n">
@@ -8967,7 +9071,7 @@
       </c>
     </row>
     <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="4" t="n">
+      <c r="A263" s="5" t="n">
         <v>33878</v>
       </c>
       <c r="B263" s="1" t="n">
@@ -9000,7 +9104,7 @@
       </c>
     </row>
     <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="4" t="n">
+      <c r="A264" s="5" t="n">
         <v>33909</v>
       </c>
       <c r="B264" s="1" t="n">
@@ -9033,7 +9137,7 @@
       </c>
     </row>
     <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="4" t="n">
+      <c r="A265" s="5" t="n">
         <v>33939</v>
       </c>
       <c r="B265" s="1" t="n">
@@ -9066,7 +9170,7 @@
       </c>
     </row>
     <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="4" t="n">
+      <c r="A266" s="5" t="n">
         <v>33970</v>
       </c>
       <c r="B266" s="1" t="n">
@@ -9099,7 +9203,7 @@
       </c>
     </row>
     <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="4" t="n">
+      <c r="A267" s="5" t="n">
         <v>34001</v>
       </c>
       <c r="B267" s="1" t="n">
@@ -9132,7 +9236,7 @@
       </c>
     </row>
     <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="4" t="n">
+      <c r="A268" s="5" t="n">
         <v>34029</v>
       </c>
       <c r="B268" s="1" t="n">
@@ -9165,7 +9269,7 @@
       </c>
     </row>
     <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="4" t="n">
+      <c r="A269" s="5" t="n">
         <v>34060</v>
       </c>
       <c r="B269" s="1" t="n">
@@ -9198,7 +9302,7 @@
       </c>
     </row>
     <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="4" t="n">
+      <c r="A270" s="5" t="n">
         <v>34090</v>
       </c>
       <c r="B270" s="1" t="n">
@@ -9231,7 +9335,7 @@
       </c>
     </row>
     <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="4" t="n">
+      <c r="A271" s="5" t="n">
         <v>34121</v>
       </c>
       <c r="B271" s="1" t="n">
@@ -9264,7 +9368,7 @@
       </c>
     </row>
     <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="4" t="n">
+      <c r="A272" s="5" t="n">
         <v>34151</v>
       </c>
       <c r="B272" s="1" t="n">
@@ -9297,7 +9401,7 @@
       </c>
     </row>
     <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="4" t="n">
+      <c r="A273" s="5" t="n">
         <v>34182</v>
       </c>
       <c r="B273" s="1" t="n">
@@ -9330,7 +9434,7 @@
       </c>
     </row>
     <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="4" t="n">
+      <c r="A274" s="5" t="n">
         <v>34213</v>
       </c>
       <c r="B274" s="1" t="n">
@@ -9363,7 +9467,7 @@
       </c>
     </row>
     <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="4" t="n">
+      <c r="A275" s="5" t="n">
         <v>34243</v>
       </c>
       <c r="B275" s="1" t="n">
@@ -9396,7 +9500,7 @@
       </c>
     </row>
     <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="4" t="n">
+      <c r="A276" s="5" t="n">
         <v>34274</v>
       </c>
       <c r="B276" s="1" t="n">
@@ -9429,7 +9533,7 @@
       </c>
     </row>
     <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="4" t="n">
+      <c r="A277" s="5" t="n">
         <v>34304</v>
       </c>
       <c r="B277" s="1" t="n">
@@ -9462,7 +9566,7 @@
       </c>
     </row>
     <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="4" t="n">
+      <c r="A278" s="5" t="n">
         <v>34335</v>
       </c>
       <c r="B278" s="1" t="n">
@@ -9495,7 +9599,7 @@
       </c>
     </row>
     <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="4" t="n">
+      <c r="A279" s="5" t="n">
         <v>34366</v>
       </c>
       <c r="B279" s="1" t="n">
@@ -9528,7 +9632,7 @@
       </c>
     </row>
     <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="4" t="n">
+      <c r="A280" s="5" t="n">
         <v>34394</v>
       </c>
       <c r="B280" s="1" t="n">
@@ -9561,7 +9665,7 @@
       </c>
     </row>
     <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="4" t="n">
+      <c r="A281" s="5" t="n">
         <v>34425</v>
       </c>
       <c r="B281" s="1" t="n">
@@ -9594,7 +9698,7 @@
       </c>
     </row>
     <row r="282" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="4" t="n">
+      <c r="A282" s="5" t="n">
         <v>34455</v>
       </c>
       <c r="B282" s="1" t="n">
@@ -9627,7 +9731,7 @@
       </c>
     </row>
     <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="4" t="n">
+      <c r="A283" s="5" t="n">
         <v>34486</v>
       </c>
       <c r="B283" s="1" t="n">
@@ -9660,7 +9764,7 @@
       </c>
     </row>
     <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="4" t="n">
+      <c r="A284" s="5" t="n">
         <v>34516</v>
       </c>
       <c r="B284" s="1" t="n">
@@ -9693,7 +9797,7 @@
       </c>
     </row>
     <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="4" t="n">
+      <c r="A285" s="5" t="n">
         <v>34547</v>
       </c>
       <c r="B285" s="1" t="n">
@@ -9726,7 +9830,7 @@
       </c>
     </row>
     <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="4" t="n">
+      <c r="A286" s="5" t="n">
         <v>34578</v>
       </c>
       <c r="B286" s="1" t="n">
@@ -9759,7 +9863,7 @@
       </c>
     </row>
     <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="4" t="n">
+      <c r="A287" s="5" t="n">
         <v>34608</v>
       </c>
       <c r="B287" s="1" t="n">
@@ -9792,7 +9896,7 @@
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="4" t="n">
+      <c r="A288" s="5" t="n">
         <v>34639</v>
       </c>
       <c r="B288" s="1" t="n">
@@ -9825,7 +9929,7 @@
       </c>
     </row>
     <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="4" t="n">
+      <c r="A289" s="5" t="n">
         <v>34669</v>
       </c>
       <c r="B289" s="1" t="n">
@@ -9858,7 +9962,7 @@
       </c>
     </row>
     <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="4" t="n">
+      <c r="A290" s="5" t="n">
         <v>34700</v>
       </c>
       <c r="B290" s="1" t="n">
@@ -9891,7 +9995,7 @@
       </c>
     </row>
     <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="4" t="n">
+      <c r="A291" s="5" t="n">
         <v>34731</v>
       </c>
       <c r="B291" s="1" t="n">
@@ -9924,7 +10028,7 @@
       </c>
     </row>
     <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="4" t="n">
+      <c r="A292" s="5" t="n">
         <v>34759</v>
       </c>
       <c r="B292" s="1" t="n">
@@ -9957,7 +10061,7 @@
       </c>
     </row>
     <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="4" t="n">
+      <c r="A293" s="5" t="n">
         <v>34790</v>
       </c>
       <c r="B293" s="1" t="n">
@@ -9990,7 +10094,7 @@
       </c>
     </row>
     <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="4" t="n">
+      <c r="A294" s="5" t="n">
         <v>34820</v>
       </c>
       <c r="B294" s="1" t="n">
@@ -10023,7 +10127,7 @@
       </c>
     </row>
     <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="4" t="n">
+      <c r="A295" s="5" t="n">
         <v>34851</v>
       </c>
       <c r="B295" s="1" t="n">
@@ -10056,7 +10160,7 @@
       </c>
     </row>
     <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="4" t="n">
+      <c r="A296" s="5" t="n">
         <v>34881</v>
       </c>
       <c r="B296" s="1" t="n">
@@ -10089,7 +10193,7 @@
       </c>
     </row>
     <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="4" t="n">
+      <c r="A297" s="5" t="n">
         <v>34912</v>
       </c>
       <c r="B297" s="1" t="n">
@@ -10122,7 +10226,7 @@
       </c>
     </row>
     <row r="298" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="4" t="n">
+      <c r="A298" s="5" t="n">
         <v>34943</v>
       </c>
       <c r="B298" s="1" t="n">
@@ -10155,7 +10259,7 @@
       </c>
     </row>
     <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="4" t="n">
+      <c r="A299" s="5" t="n">
         <v>34973</v>
       </c>
       <c r="B299" s="1" t="n">
@@ -10188,7 +10292,7 @@
       </c>
     </row>
     <row r="300" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="4" t="n">
+      <c r="A300" s="5" t="n">
         <v>35004</v>
       </c>
       <c r="B300" s="1" t="n">
@@ -10221,7 +10325,7 @@
       </c>
     </row>
     <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="4" t="n">
+      <c r="A301" s="5" t="n">
         <v>35034</v>
       </c>
       <c r="B301" s="1" t="n">
@@ -10254,7 +10358,7 @@
       </c>
     </row>
     <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="4" t="n">
+      <c r="A302" s="5" t="n">
         <v>35065</v>
       </c>
       <c r="B302" s="1" t="n">
@@ -10287,7 +10391,7 @@
       </c>
     </row>
     <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="4" t="n">
+      <c r="A303" s="5" t="n">
         <v>35096</v>
       </c>
       <c r="B303" s="1" t="n">
@@ -10320,7 +10424,7 @@
       </c>
     </row>
     <row r="304" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="4" t="n">
+      <c r="A304" s="5" t="n">
         <v>35125</v>
       </c>
       <c r="B304" s="1" t="n">
@@ -10353,7 +10457,7 @@
       </c>
     </row>
     <row r="305" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="4" t="n">
+      <c r="A305" s="5" t="n">
         <v>35156</v>
       </c>
       <c r="B305" s="1" t="n">
@@ -10386,7 +10490,7 @@
       </c>
     </row>
     <row r="306" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="4" t="n">
+      <c r="A306" s="5" t="n">
         <v>35186</v>
       </c>
       <c r="B306" s="1" t="n">
@@ -10419,7 +10523,7 @@
       </c>
     </row>
     <row r="307" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="4" t="n">
+      <c r="A307" s="5" t="n">
         <v>35217</v>
       </c>
       <c r="B307" s="1" t="n">
@@ -10452,7 +10556,7 @@
       </c>
     </row>
     <row r="308" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="4" t="n">
+      <c r="A308" s="5" t="n">
         <v>35247</v>
       </c>
       <c r="B308" s="1" t="n">
@@ -10485,7 +10589,7 @@
       </c>
     </row>
     <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="4" t="n">
+      <c r="A309" s="5" t="n">
         <v>35278</v>
       </c>
       <c r="B309" s="1" t="n">
@@ -10518,7 +10622,7 @@
       </c>
     </row>
     <row r="310" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="4" t="n">
+      <c r="A310" s="5" t="n">
         <v>35309</v>
       </c>
       <c r="B310" s="1" t="n">
@@ -10551,7 +10655,7 @@
       </c>
     </row>
     <row r="311" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="4" t="n">
+      <c r="A311" s="5" t="n">
         <v>35339</v>
       </c>
       <c r="B311" s="1" t="n">
@@ -10584,7 +10688,7 @@
       </c>
     </row>
     <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="4" t="n">
+      <c r="A312" s="5" t="n">
         <v>35370</v>
       </c>
       <c r="B312" s="1" t="n">
@@ -10617,7 +10721,7 @@
       </c>
     </row>
     <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="4" t="n">
+      <c r="A313" s="5" t="n">
         <v>35400</v>
       </c>
       <c r="B313" s="1" t="n">
@@ -10650,7 +10754,7 @@
       </c>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="4" t="n">
+      <c r="A314" s="5" t="n">
         <v>35431</v>
       </c>
       <c r="B314" s="1" t="n">
@@ -10683,7 +10787,7 @@
       </c>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="4" t="n">
+      <c r="A315" s="5" t="n">
         <v>35462</v>
       </c>
       <c r="B315" s="1" t="n">
@@ -10716,7 +10820,7 @@
       </c>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="4" t="n">
+      <c r="A316" s="5" t="n">
         <v>35490</v>
       </c>
       <c r="B316" s="1" t="n">
@@ -10749,7 +10853,7 @@
       </c>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="4" t="n">
+      <c r="A317" s="5" t="n">
         <v>35521</v>
       </c>
       <c r="B317" s="1" t="n">
@@ -10782,7 +10886,7 @@
       </c>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="4" t="n">
+      <c r="A318" s="5" t="n">
         <v>35551</v>
       </c>
       <c r="B318" s="1" t="n">
@@ -10815,7 +10919,7 @@
       </c>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="4" t="n">
+      <c r="A319" s="5" t="n">
         <v>35582</v>
       </c>
       <c r="B319" s="1" t="n">
@@ -10848,7 +10952,7 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="4" t="n">
+      <c r="A320" s="5" t="n">
         <v>35612</v>
       </c>
       <c r="B320" s="1" t="n">
@@ -10881,7 +10985,7 @@
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="4" t="n">
+      <c r="A321" s="5" t="n">
         <v>35643</v>
       </c>
       <c r="B321" s="1" t="n">
@@ -10914,7 +11018,7 @@
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="4" t="n">
+      <c r="A322" s="5" t="n">
         <v>35674</v>
       </c>
       <c r="B322" s="1" t="n">
@@ -10947,7 +11051,7 @@
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="4" t="n">
+      <c r="A323" s="5" t="n">
         <v>35704</v>
       </c>
       <c r="B323" s="1" t="n">
@@ -10980,7 +11084,7 @@
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="4" t="n">
+      <c r="A324" s="5" t="n">
         <v>35735</v>
       </c>
       <c r="B324" s="1" t="n">
@@ -11013,7 +11117,7 @@
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="4" t="n">
+      <c r="A325" s="5" t="n">
         <v>35765</v>
       </c>
       <c r="B325" s="1" t="n">
@@ -11046,7 +11150,7 @@
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="4" t="n">
+      <c r="A326" s="5" t="n">
         <v>35796</v>
       </c>
       <c r="B326" s="1" t="n">
@@ -11079,7 +11183,7 @@
       </c>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="4" t="n">
+      <c r="A327" s="5" t="n">
         <v>35827</v>
       </c>
       <c r="B327" s="1" t="n">
@@ -11112,7 +11216,7 @@
       </c>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="4" t="n">
+      <c r="A328" s="5" t="n">
         <v>35855</v>
       </c>
       <c r="B328" s="1" t="n">
@@ -11145,7 +11249,7 @@
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="4" t="n">
+      <c r="A329" s="5" t="n">
         <v>35886</v>
       </c>
       <c r="B329" s="1" t="n">
@@ -11178,7 +11282,7 @@
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="4" t="n">
+      <c r="A330" s="5" t="n">
         <v>35916</v>
       </c>
       <c r="B330" s="1" t="n">
@@ -11211,7 +11315,7 @@
       </c>
     </row>
     <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="4" t="n">
+      <c r="A331" s="5" t="n">
         <v>35947</v>
       </c>
       <c r="B331" s="1" t="n">
@@ -11244,7 +11348,7 @@
       </c>
     </row>
     <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="4" t="n">
+      <c r="A332" s="5" t="n">
         <v>35977</v>
       </c>
       <c r="B332" s="1" t="n">
@@ -11277,7 +11381,7 @@
       </c>
     </row>
     <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="4" t="n">
+      <c r="A333" s="5" t="n">
         <v>36008</v>
       </c>
       <c r="B333" s="1" t="n">
@@ -11310,7 +11414,7 @@
       </c>
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="4" t="n">
+      <c r="A334" s="5" t="n">
         <v>36039</v>
       </c>
       <c r="B334" s="1" t="n">
@@ -11343,7 +11447,7 @@
       </c>
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="4" t="n">
+      <c r="A335" s="5" t="n">
         <v>36069</v>
       </c>
       <c r="B335" s="1" t="n">
@@ -11376,7 +11480,7 @@
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="4" t="n">
+      <c r="A336" s="5" t="n">
         <v>36100</v>
       </c>
       <c r="B336" s="1" t="n">
@@ -11409,7 +11513,7 @@
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="4" t="n">
+      <c r="A337" s="5" t="n">
         <v>36130</v>
       </c>
       <c r="B337" s="1" t="n">
@@ -11442,7 +11546,7 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="4" t="n">
+      <c r="A338" s="5" t="n">
         <v>36161</v>
       </c>
       <c r="B338" s="1" t="n">
@@ -11475,7 +11579,7 @@
       </c>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="4" t="n">
+      <c r="A339" s="5" t="n">
         <v>36192</v>
       </c>
       <c r="B339" s="1" t="n">
@@ -11508,7 +11612,7 @@
       </c>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="4" t="n">
+      <c r="A340" s="5" t="n">
         <v>36220</v>
       </c>
       <c r="B340" s="1" t="n">
@@ -11541,7 +11645,7 @@
       </c>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="4" t="n">
+      <c r="A341" s="5" t="n">
         <v>36251</v>
       </c>
       <c r="B341" s="1" t="n">
@@ -11574,7 +11678,7 @@
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="4" t="n">
+      <c r="A342" s="5" t="n">
         <v>36281</v>
       </c>
       <c r="B342" s="1" t="n">
@@ -11607,7 +11711,7 @@
       </c>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="4" t="n">
+      <c r="A343" s="5" t="n">
         <v>36312</v>
       </c>
       <c r="B343" s="1" t="n">
@@ -11640,7 +11744,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="4" t="n">
+      <c r="A344" s="5" t="n">
         <v>36342</v>
       </c>
       <c r="B344" s="1" t="n">
@@ -11673,7 +11777,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="4" t="n">
+      <c r="A345" s="5" t="n">
         <v>36373</v>
       </c>
       <c r="B345" s="1" t="n">
@@ -11706,7 +11810,7 @@
       </c>
     </row>
     <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="4" t="n">
+      <c r="A346" s="5" t="n">
         <v>36404</v>
       </c>
       <c r="B346" s="1" t="n">
@@ -11739,7 +11843,7 @@
       </c>
     </row>
     <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="4" t="n">
+      <c r="A347" s="5" t="n">
         <v>36434</v>
       </c>
       <c r="B347" s="1" t="n">
@@ -11772,7 +11876,7 @@
       </c>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="4" t="n">
+      <c r="A348" s="5" t="n">
         <v>36465</v>
       </c>
       <c r="B348" s="1" t="n">
@@ -11805,7 +11909,7 @@
       </c>
     </row>
     <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="4" t="n">
+      <c r="A349" s="5" t="n">
         <v>36495</v>
       </c>
       <c r="B349" s="1" t="n">
@@ -11838,7 +11942,7 @@
       </c>
     </row>
     <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="4" t="n">
+      <c r="A350" s="5" t="n">
         <v>36526</v>
       </c>
       <c r="B350" s="1" t="n">
@@ -11871,7 +11975,7 @@
       </c>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="4" t="n">
+      <c r="A351" s="5" t="n">
         <v>36557</v>
       </c>
       <c r="B351" s="1" t="n">
@@ -11904,7 +12008,7 @@
       </c>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="4" t="n">
+      <c r="A352" s="5" t="n">
         <v>36586</v>
       </c>
       <c r="B352" s="1" t="n">
@@ -11937,7 +12041,7 @@
       </c>
     </row>
     <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="4" t="n">
+      <c r="A353" s="5" t="n">
         <v>36617</v>
       </c>
       <c r="B353" s="1" t="n">
@@ -11970,7 +12074,7 @@
       </c>
     </row>
     <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="4" t="n">
+      <c r="A354" s="5" t="n">
         <v>36647</v>
       </c>
       <c r="B354" s="1" t="n">
@@ -12003,7 +12107,7 @@
       </c>
     </row>
     <row r="355" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="4" t="n">
+      <c r="A355" s="5" t="n">
         <v>36678</v>
       </c>
       <c r="B355" s="1" t="n">
@@ -12036,7 +12140,7 @@
       </c>
     </row>
     <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="4" t="n">
+      <c r="A356" s="5" t="n">
         <v>36708</v>
       </c>
       <c r="B356" s="1" t="n">
@@ -12069,7 +12173,7 @@
       </c>
     </row>
     <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="4" t="n">
+      <c r="A357" s="5" t="n">
         <v>36739</v>
       </c>
       <c r="B357" s="1" t="n">
@@ -12102,7 +12206,7 @@
       </c>
     </row>
     <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="4" t="n">
+      <c r="A358" s="5" t="n">
         <v>36770</v>
       </c>
       <c r="B358" s="1" t="n">
@@ -12135,7 +12239,7 @@
       </c>
     </row>
     <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="4" t="n">
+      <c r="A359" s="5" t="n">
         <v>36800</v>
       </c>
       <c r="B359" s="1" t="n">
@@ -12168,7 +12272,7 @@
       </c>
     </row>
     <row r="360" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="4" t="n">
+      <c r="A360" s="5" t="n">
         <v>36831</v>
       </c>
       <c r="B360" s="1" t="n">
@@ -12201,7 +12305,7 @@
       </c>
     </row>
     <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="4" t="n">
+      <c r="A361" s="5" t="n">
         <v>36861</v>
       </c>
       <c r="B361" s="1" t="n">
@@ -12245,23 +12349,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="35.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="n">
@@ -12270,7 +12374,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="n">
@@ -12279,24 +12383,24 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <f aca="false">C2/C3</f>
         <v>0.128251396522217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6"/>
+      <c r="B5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="n">
@@ -12305,72 +12409,73 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <f aca="false">STDEV(Data!K2:K361)</f>
         <v>0.0307130967387096</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <f aca="false">C7/C8</f>
         <v>0.116589784605477</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <f aca="false">SLOPE(Data!K2:K361,Data!G2:G361)</f>
         <v>-0.194966881553934</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <f aca="false">INTERCEPT(Data!K2:K361,Data!G2:G361)</f>
         <v>0.00472978399782408</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <f aca="false">C11 / SQRT( C8^2 - C10^2*C3^2)</f>
         <v>0.161000164109882</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <f aca="false">SQRT(C4^2 + C12^2)</f>
         <v>0.205838464707907</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -12379,67 +12484,68 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="10" t="n">
         <f aca="false">PRODUCT('At 1% exc return vol'!C2:C361)</f>
         <v>10.8119316147417</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="0" t="s">
+      <c r="G23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="0" t="s">
+      <c r="H23" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="1" t="n">
         <f aca="false">C2</f>
         <v>0.00589305555555556</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G24" s="1" t="n">
         <f aca="false">C3^2</f>
         <v>0.00211133362852058</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="8" t="n">
         <f aca="false">C3*C8*CORREL(Data!G2:G361,Data!K2:K361)</f>
         <v>-0.000411640133472609</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="1" t="n">
         <f aca="false">C7</f>
         <v>0.00358083333333333</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G25" s="1" t="n">
@@ -12453,24 +12559,25 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="7" t="n">
         <f aca="false" t="array" ref="C27:C28">MMULT(MINVERSE(G24:H25),D24:D25)</f>
-        <v>3.85964738746478</v>
+        <v>3.85964738746479</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="7" t="n">
         <v>5.48038829158666</v>
       </c>
     </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="1" t="n">
@@ -12479,7 +12586,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="1" t="n">
@@ -12487,8 +12594,9 @@
         <v>0.586763100260794</v>
       </c>
     </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C33" s="1" t="n">
@@ -12497,7 +12605,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C34" s="1" t="n">
@@ -12506,19 +12614,20 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C35" s="7" t="n">
         <f aca="false">C33/C34</f>
         <v>0.205838464707906</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="2" t="s">
         <v>37</v>
       </c>
     </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="1" t="n">
@@ -12527,10 +12636,10 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="10" t="n">
         <f aca="false">PRODUCT('At 1% exc return vol'!G2:G361)</f>
         <v>14.2620292807815</v>
       </c>
@@ -12547,36 +12656,36 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G361"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="55.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="41.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="55.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="2" t="s">
         <v>40</v>
       </c>
     </row>

--- a/Module 3/Week 11 - Short sales and dollar-neutral strategies/Example with value and growth stocks.xlsx
+++ b/Module 3/Week 11 - Short sales and dollar-neutral strategies/Example with value and growth stocks.xlsx
@@ -1,183 +1,201 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t xml:space="preserve">Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk-free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="5">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="5">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -185,6403 +203,6293 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E361"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="8.68"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Risk-free</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
         <v>25934</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="1" t="n">
         <v>0.0038</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="1" t="n">
         <v>0.0521</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.06509999999999999</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" s="1" t="n">
+        <v>0.0651</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>0.0506</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
         <v>25965</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="1" t="n">
         <v>0.0033</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="1" t="n">
         <v>0.0174</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="1" t="n">
         <v>0.0209</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="1" t="n">
         <v>0.0253</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
         <v>25993</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="1" t="n">
         <v>0.0442</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="1" t="n">
         <v>0.0245</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="1" t="n">
         <v>0.0605</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>26024</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="1" t="n">
         <v>0.0028</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="1" t="n">
         <v>0.0343</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="1" t="n">
         <v>0.0495</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="1" t="n">
         <v>0.0385</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
         <v>26054</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="1" t="n">
         <v>0.0029</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="1" t="n">
         <v>-0.037</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="1" t="n">
         <v>-0.0472</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="1" t="n">
         <v>-0.0287</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
         <v>26085</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="1" t="n">
         <v>0.0028</v>
       </c>
-      <c r="D7" t="n">
-        <v>-0.004099999999999999</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" s="1" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>0.0108</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
         <v>26115</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C8" t="n">
-        <v>-0.04090000000000001</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8" s="1" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>-0.0516</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="1" t="n">
         <v>-0.0423</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
         <v>26146</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.04260000000000001</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C9" s="1" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>0.0803</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
         <v>26177</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="1" t="n">
         <v>-0.0049</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="1" t="n">
         <v>-0.0241</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="1" t="n">
         <v>0.0039</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
         <v>26207</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="1" t="n">
         <v>-0.0405</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="1" t="n">
         <v>-0.0484</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="1" t="n">
         <v>-0.04</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
         <v>26238</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C12" t="n">
-        <v>-0.0008999999999999998</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" s="1" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>-0.0203</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="1" t="n">
         <v>0.0069</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
         <v>26268</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.09079999999999999</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" s="1" t="n">
+        <v>0.0908</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="1" t="n">
         <v>0.0915</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
         <v>26299</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="1" t="n">
         <v>0.0029</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.06480000000000001</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" s="1" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>0.0293</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
         <v>26330</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="1" t="n">
         <v>0.0025</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="1" t="n">
         <v>0.0312</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="1" t="n">
         <v>0.0141</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.04559999999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="E15" s="1" t="n">
+        <v>0.0456</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
         <v>26359</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="1" t="n">
         <v>0.0027</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="1" t="n">
         <v>0.0089</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="1" t="n">
         <v>0.0058</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="1" t="n">
         <v>0.0216</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
         <v>26390</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="1" t="n">
         <v>0.0029</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="1" t="n">
         <v>0.0058</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.009300000000000001</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="D17" s="1" t="n">
+        <v>0.0093</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.0079</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
         <v>26420</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="1" t="n">
         <v>0.0159</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="1" t="n">
         <v>-0.0186</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="1" t="n">
         <v>0.0276</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
         <v>26451</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="1" t="n">
         <v>0.0029</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="1" t="n">
         <v>-0.0214</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="1" t="n">
         <v>-0.0552</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="1" t="n">
         <v>-0.0121</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
         <v>26481</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="1" t="n">
         <v>0.0031</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="1" t="n">
         <v>-0.0049</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="1" t="n">
         <v>-0.0129</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="1" t="n">
         <v>0.0036</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
         <v>26512</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="1" t="n">
         <v>0.0029</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="1" t="n">
         <v>0.0356</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="1" t="n">
         <v>0.0658</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="1" t="n">
         <v>0.0139</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
         <v>26543</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="1" t="n">
         <v>0.0034</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="1" t="n">
         <v>-0.008</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="1" t="n">
         <v>-0.0027</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="1" t="n">
         <v>-0.006</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
         <v>26573</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="1" t="n">
         <v>0.0092</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="1" t="n">
         <v>0.0125</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="1" t="n">
         <v>0.004</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
         <v>26604</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="1" t="n">
         <v>0.0497</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="1" t="n">
         <v>0.0924</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="1" t="n">
         <v>0.0299</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
         <v>26634</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-0.008100000000000001</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="C25" s="1" t="n">
+        <v>0.0099</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>0.0251</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
         <v>26665</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="1" t="n">
         <v>-0.0283</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="1" t="n">
         <v>-0.0177</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="1" t="n">
         <v>-0.0281</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
         <v>26696</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="1" t="n">
         <v>-0.0443</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="1" t="n">
         <v>-0.0506</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="1" t="n">
         <v>-0.0331</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>26724</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C28" t="n">
-        <v>-0.008399999999999999</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.009399999999999999</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="C28" s="1" t="n">
+        <v>-0.0084</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>-0.0132</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
         <v>26755</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="1" t="n">
         <v>0.0052</v>
       </c>
-      <c r="C29" t="n">
-        <v>-0.05160000000000001</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="C29" s="1" t="n">
+        <v>-0.0516</v>
+      </c>
+      <c r="D29" s="1" t="n">
         <v>-0.0184</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="1" t="n">
         <v>-0.0622</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
         <v>26785</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="1" t="n">
         <v>-0.0246</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="1" t="n">
         <v>-0.0384</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="1" t="n">
         <v>-0.0118</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
         <v>26816</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="1" t="n">
         <v>-0.0106</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="1" t="n">
         <v>-0.0109</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="1" t="n">
         <v>-0.0101</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
         <v>26846</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="1" t="n">
         <v>0.0064</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="1" t="n">
         <v>0.0591</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="1" t="n">
         <v>0.0702</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
         <v>26877</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="1" t="n">
         <v>-0.0312</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="1" t="n">
         <v>-0.0164</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="1" t="n">
         <v>-0.0326</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
         <v>26908</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="1" t="n">
         <v>0.0068</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="1" t="n">
         <v>0.0542</v>
       </c>
-      <c r="D34" t="n">
-        <v>0.08990000000000001</v>
-      </c>
-      <c r="E34" t="n">
+      <c r="D34" s="1" t="n">
+        <v>0.0899</v>
+      </c>
+      <c r="E34" s="1" t="n">
         <v>0.0273</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
         <v>26938</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="1" t="n">
         <v>0.0065</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="1" t="n">
         <v>-0.0018</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="1" t="n">
         <v>0.0008</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="1" t="n">
         <v>-0.0029</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
         <v>26969</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="1" t="n">
         <v>0.0056</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="1" t="n">
         <v>-0.1222</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="1" t="n">
         <v>-0.1199</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="1" t="n">
         <v>-0.1309</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
         <v>26999</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="1" t="n">
         <v>0.0064</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="1" t="n">
         <v>0.0123</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="1" t="n">
         <v>0.044</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="1" t="n">
         <v>-0.0126</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
         <v>27030</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="1" t="n">
         <v>0.0063</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="1" t="n">
         <v>0.0629</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="1" t="n">
         <v>-0.0061</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
         <v>27061</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="1" t="n">
         <v>0.0058</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="1" t="n">
         <v>0.0012</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="1" t="n">
         <v>0.0209</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="1" t="n">
         <v>-0.0098</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
         <v>27089</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="1" t="n">
         <v>0.0056</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="1" t="n">
         <v>-0.0226</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="1" t="n">
         <v>-0.0217</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="1" t="n">
         <v>-0.0166</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
         <v>27120</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="1" t="n">
         <v>-0.0453</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="1" t="n">
         <v>-0.0414</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="1" t="n">
         <v>-0.0355</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
         <v>27150</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="1" t="n">
         <v>-0.0395</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="1" t="n">
         <v>-0.0635</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="1" t="n">
         <v>-0.0213</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
         <v>27181</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="1" t="n">
         <v>-0.0224</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="1" t="n">
         <v>-0.0222</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="1" t="n">
         <v>-0.0218</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
         <v>27211</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="1" t="n">
         <v>-0.0736</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="1" t="n">
         <v>-0.0288</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="1" t="n">
         <v>-0.0925</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
         <v>27242</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="C45" t="n">
-        <v>-0.08789999999999999</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="C45" s="1" t="n">
+        <v>-0.0879</v>
+      </c>
+      <c r="D45" s="1" t="n">
         <v>-0.0723</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="1" t="n">
         <v>-0.1008</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="n">
         <v>27273</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="1" t="n">
         <v>0.0081</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="1" t="n">
         <v>-0.1098</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="1" t="n">
         <v>-0.0726</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="1" t="n">
         <v>-0.1373</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="n">
         <v>27303</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="1" t="n">
         <v>0.1662</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="1" t="n">
         <v>0.0791</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="1" t="n">
         <v>0.2099</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="n">
         <v>27334</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="1" t="n">
         <v>0.0054</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="1" t="n">
         <v>-0.0399</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="1" t="n">
         <v>-0.0443</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="1" t="n">
         <v>-0.0403</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="n">
         <v>27364</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="1" t="n">
         <v>-0.0274</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="1" t="n">
         <v>-0.0413</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="1" t="n">
         <v>-0.0342</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="n">
         <v>27395</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="1" t="n">
         <v>0.0058</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="1" t="n">
         <v>0.1425</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="1" t="n">
         <v>0.2399</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="1" t="n">
         <v>0.1113</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>27426</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C51" t="n">
-        <v>0.05989999999999999</v>
-      </c>
-      <c r="D51" t="n">
+      <c r="C51" s="1" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="D51" s="1" t="n">
         <v>0.0261</v>
       </c>
-      <c r="E51" t="n">
-        <v>0.08119999999999999</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="E51" s="1" t="n">
+        <v>0.0812</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
         <v>27454</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="1" t="n">
         <v>0.0041</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="1" t="n">
         <v>0.0307</v>
       </c>
-      <c r="D52" t="n">
-        <v>0.07530000000000001</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="D52" s="1" t="n">
+        <v>0.0753</v>
+      </c>
+      <c r="E52" s="1" t="n">
         <v>0.0313</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
         <v>27485</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="1" t="n">
         <v>0.0466</v>
       </c>
-      <c r="D53" t="n">
-        <v>0.05690000000000001</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="D53" s="1" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>0.0579</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
         <v>27515</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="1" t="n">
         <v>0.0564</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="1" t="n">
         <v>0.0585</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
         <v>27546</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="1" t="n">
         <v>0.0041</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="1" t="n">
         <v>0.0528</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="1" t="n">
         <v>0.0722</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="1" t="n">
         <v>0.0442</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
         <v>27576</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="1" t="n">
         <v>0.0048</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="1" t="n">
         <v>-0.0612</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="1" t="n">
         <v>-0.0367</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="1" t="n">
         <v>-0.0732</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
         <v>27607</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="1" t="n">
         <v>0.0048</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="1" t="n">
         <v>-0.0236</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="1" t="n">
         <v>-0.0401</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="1" t="n">
         <v>-0.0228</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
         <v>27638</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="1" t="n">
         <v>0.0053</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="1" t="n">
         <v>-0.0373</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="1" t="n">
         <v>-0.0369</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="1" t="n">
         <v>-0.0399</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
         <v>27668</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="1" t="n">
         <v>0.0056</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="1" t="n">
         <v>0.0588</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="1" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="1" t="n">
         <v>0.0633</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
         <v>27699</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="1" t="n">
         <v>0.0041</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="1" t="n">
         <v>0.0306</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="1" t="n">
         <v>0.0421</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="1" t="n">
         <v>0.0294</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
         <v>27729</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="1" t="n">
         <v>0.0048</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="1" t="n">
         <v>-0.0112</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="1" t="n">
         <v>0.0021</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="1" t="n">
         <v>-0.0178</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="n">
         <v>27760</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="1" t="n">
         <v>0.2092</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="1" t="n">
         <v>0.1104</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="n">
         <v>27791</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="1" t="n">
         <v>0.0034</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="1" t="n">
         <v>0.0065</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="1" t="n">
         <v>0.078</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="1" t="n">
         <v>-0.0102</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="n">
         <v>27820</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="1" t="n">
         <v>0.0272</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="1" t="n">
         <v>0.0206</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="1" t="n">
         <v>0.0291</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="n">
         <v>27851</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="1" t="n">
         <v>-0.0107</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="1" t="n">
         <v>-0.0148</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="1" t="n">
         <v>-0.016</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="n">
         <v>27881</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="1" t="n">
         <v>-0.0097</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="1" t="n">
         <v>-0.0181</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="1" t="n">
         <v>-0.0064</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="n">
         <v>27912</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="1" t="n">
         <v>0.0449</v>
       </c>
-      <c r="D67" t="n">
-        <v>0.05019999999999999</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="D67" s="1" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="E67" s="1" t="n">
         <v>0.0435</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="n">
         <v>27942</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="1" t="n">
         <v>-0.0059</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="1" t="n">
         <v>-0.0123</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="n">
         <v>27973</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="1" t="n">
         <v>-0.0015</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="1" t="n">
         <v>-0.011</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="1" t="n">
         <v>-0.0052</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="n">
         <v>28004</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="1" t="n">
         <v>0.0269</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="1" t="n">
         <v>0.0226</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="n">
         <v>28034</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="1" t="n">
         <v>0.0041</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="1" t="n">
         <v>-0.0201</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="1" t="n">
         <v>-0.0292</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="1" t="n">
         <v>-0.0238</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
         <v>28065</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="1" t="n">
         <v>0.0076</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="1" t="n">
         <v>0.0272</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="1" t="n">
         <v>-0.0053</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
         <v>28095</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="1" t="n">
         <v>0.0605</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="1" t="n">
         <v>0.0496</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
         <v>28126</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="1" t="n">
         <v>0.0036</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="1" t="n">
         <v>-0.0367</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="1" t="n">
         <v>0.0111</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="1" t="n">
         <v>-0.0605</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
         <v>28157</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="1" t="n">
         <v>0.0035</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="1" t="n">
         <v>-0.0159</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="1" t="n">
         <v>-0.012</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="1" t="n">
         <v>-0.0177</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
         <v>28185</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="1" t="n">
         <v>0.0038</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="1" t="n">
         <v>-0.0097</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="1" t="n">
         <v>-0.0161</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
         <v>28216</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="1" t="n">
         <v>0.0038</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="1" t="n">
         <v>0.0053</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="1" t="n">
         <v>0.036</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="1" t="n">
         <v>-0.0101</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
         <v>28246</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="1" t="n">
         <v>-0.011</v>
       </c>
-      <c r="D78" t="n">
-        <v>-0.008100000000000001</v>
-      </c>
-      <c r="E78" t="n">
+      <c r="D78" s="1" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="E78" s="1" t="n">
         <v>-0.0188</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
         <v>28277</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="1" t="n">
         <v>0.0512</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="1" t="n">
         <v>0.057</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="1" t="n">
         <v>0.0576</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
         <v>28307</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="1" t="n">
         <v>-0.0127</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="1" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="1" t="n">
         <v>-0.0145</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
         <v>28338</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="1" t="n">
         <v>-0.0132</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="1" t="n">
         <v>-0.0248</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="1" t="n">
         <v>0.0028</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
         <v>28369</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="1" t="n">
         <v>0.0016</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="1" t="n">
         <v>-0.0016</v>
       </c>
-      <c r="E82" t="n">
-        <v>-0.005699999999999999</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="E82" s="1" t="n">
+        <v>-0.0057</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
         <v>28399</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="1" t="n">
         <v>-0.039</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="1" t="n">
         <v>-0.0275</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="1" t="n">
         <v>-0.044</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
         <v>28430</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="1" t="n">
         <v>0.045</v>
       </c>
-      <c r="D84" t="n">
-        <v>0.05889999999999999</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="D84" s="1" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="E84" s="1" t="n">
         <v>0.0435</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
         <v>28460</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="1" t="n">
         <v>0.0076</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="1" t="n">
         <v>0.0132</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="1" t="n">
         <v>0.0038</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
         <v>28491</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="1" t="n">
         <v>-0.0551</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="1" t="n">
         <v>-0.0252</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="1" t="n">
         <v>-0.0633</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
         <v>28522</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C87" t="n">
-        <v>-0.009299999999999999</v>
-      </c>
-      <c r="D87" t="n">
+      <c r="C87" s="1" t="n">
+        <v>-0.0093</v>
+      </c>
+      <c r="D87" s="1" t="n">
         <v>-0.0034</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="1" t="n">
         <v>-0.0234</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="n">
         <v>28550</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="1" t="n">
         <v>0.0053</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="1" t="n">
         <v>0.0338</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="1" t="n">
         <v>0.0503</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="1" t="n">
         <v>0.0255</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="n">
         <v>28581</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" s="1" t="n">
         <v>0.0054</v>
       </c>
-      <c r="C89" t="n">
-        <v>0.08410000000000001</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="E89" t="n">
+      <c r="C89" s="1" t="n">
+        <v>0.0841</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="E89" s="1" t="n">
         <v>0.11</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="n">
         <v>28611</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="1" t="n">
         <v>0.0227</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="1" t="n">
         <v>0.023</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="n">
         <v>28642</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="1" t="n">
         <v>0.0054</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="1" t="n">
         <v>-0.0115</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="1" t="n">
         <v>-0.0086</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="1" t="n">
         <v>-0.0134</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="n">
         <v>28672</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="1" t="n">
         <v>0.0056</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="1" t="n">
         <v>0.0594</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="1" t="n">
         <v>0.0699</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="n">
         <v>28703</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="1" t="n">
         <v>0.0056</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="1" t="n">
         <v>0.0434</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="1" t="n">
         <v>0.0361</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="1" t="n">
         <v>0.0405</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="n">
         <v>28734</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="1" t="n">
         <v>0.0062</v>
       </c>
-      <c r="C94" t="n">
-        <v>-0.008199999999999999</v>
-      </c>
-      <c r="D94" t="n">
+      <c r="C94" s="1" t="n">
+        <v>-0.0082</v>
+      </c>
+      <c r="D94" s="1" t="n">
         <v>-0.0021</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="1" t="n">
         <v>-0.0254</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="n">
         <v>28764</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="1" t="n">
         <v>0.0068</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="1" t="n">
         <v>-0.1122</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="1" t="n">
         <v>-0.1341</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" s="1" t="n">
         <v>-0.1126</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="n">
         <v>28795</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="1" t="n">
         <v>0.0334</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" s="1" t="n">
         <v>0.0341</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="n">
         <v>28825</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="1" t="n">
         <v>0.0078</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="1" t="n">
         <v>0.0019</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="1" t="n">
         <v>0.0284</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="n">
         <v>28856</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="1" t="n">
         <v>0.0077</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="1" t="n">
         <v>0.0499</v>
       </c>
-      <c r="D98" t="n">
-        <v>0.07400000000000001</v>
-      </c>
-      <c r="E98" t="n">
+      <c r="D98" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="E98" s="1" t="n">
         <v>0.0387</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="n">
         <v>28887</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="1" t="n">
         <v>0.0073</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="1" t="n">
         <v>-0.0283</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="1" t="n">
         <v>-0.0263</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="1" t="n">
         <v>-0.0367</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="n">
         <v>28915</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="1" t="n">
         <v>0.0081</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="1" t="n">
         <v>0.0648</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="1" t="n">
         <v>0.0775</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" s="1" t="n">
         <v>0.0635</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="n">
         <v>28946</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="1" t="n">
         <v>0.0073</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="1" t="n">
         <v>0.0131</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="1" t="n">
         <v>0.0027</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
         <v>28976</v>
       </c>
-      <c r="B102" t="n">
-        <v>0.008200000000000001</v>
-      </c>
-      <c r="C102" t="n">
+      <c r="B102" s="1" t="n">
+        <v>0.0082</v>
+      </c>
+      <c r="C102" s="1" t="n">
         <v>-0.0138</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="1" t="n">
         <v>-0.0111</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" s="1" t="n">
         <v>-0.019</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
         <v>29007</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="1" t="n">
         <v>0.0081</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="1" t="n">
         <v>0.0574</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" s="1" t="n">
         <v>0.0339</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
         <v>29037</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="1" t="n">
         <v>0.0077</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="1" t="n">
         <v>0.0305</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" s="1" t="n">
         <v>0.0075</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
         <v>29068</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="1" t="n">
         <v>0.0077</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="1" t="n">
         <v>0.0631</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="1" t="n">
         <v>0.0576</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" s="1" t="n">
         <v>0.0706</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
         <v>29099</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="1" t="n">
         <v>0.0083</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="1" t="n">
         <v>-0.0077</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" s="1" t="n">
         <v>-0.006</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
         <v>29129</v>
       </c>
-      <c r="B107" t="n">
-        <v>0.008699999999999999</v>
-      </c>
-      <c r="C107" t="n">
+      <c r="B107" s="1" t="n">
+        <v>0.0087</v>
+      </c>
+      <c r="C107" s="1" t="n">
         <v>-0.0723</v>
       </c>
-      <c r="D107" t="n">
-        <v>-0.08939999999999999</v>
-      </c>
-      <c r="E107" t="n">
+      <c r="D107" s="1" t="n">
+        <v>-0.0894</v>
+      </c>
+      <c r="E107" s="1" t="n">
         <v>-0.0704</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="n">
         <v>29160</v>
       </c>
-      <c r="B108" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="C108" t="n">
+      <c r="B108" s="1" t="n">
+        <v>0.0099</v>
+      </c>
+      <c r="C108" s="1" t="n">
         <v>0.0621</v>
       </c>
-      <c r="D108" t="n">
-        <v>0.04650000000000001</v>
-      </c>
-      <c r="E108" t="n">
+      <c r="D108" s="1" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="E108" s="1" t="n">
         <v>0.0698</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="n">
         <v>29190</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="1" t="n">
         <v>0.0095</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109" s="1" t="n">
         <v>0.0273</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="1" t="n">
         <v>0.0256</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" s="1" t="n">
         <v>0.0364</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="n">
         <v>29221</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" s="1" t="n">
         <v>0.063</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="1" t="n">
         <v>0.0799</v>
       </c>
-      <c r="E110" t="n">
-        <v>0.05230000000000001</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="E110" s="1" t="n">
+        <v>0.0523</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="n">
         <v>29252</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="1" t="n">
         <v>0.0089</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" s="1" t="n">
         <v>-0.0034</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="1" t="n">
         <v>-0.0022</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" s="1" t="n">
         <v>-0.0273</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="n">
         <v>29281</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="1" t="n">
         <v>0.0121</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112" s="1" t="n">
         <v>-0.1169</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="1" t="n">
         <v>-0.1399</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" s="1" t="n">
         <v>-0.1049</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="n">
         <v>29312</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="1" t="n">
         <v>0.0126</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113" s="1" t="n">
         <v>0.0521</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="1" t="n">
         <v>0.0613</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" s="1" t="n">
         <v>0.0418</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="n">
         <v>29342</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="1" t="n">
         <v>0.0081</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" s="1" t="n">
         <v>0.0607</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="1" t="n">
         <v>0.0682</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" s="1" t="n">
         <v>0.0603</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="n">
         <v>29373</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" s="1" t="n">
         <v>0.0061</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" s="1" t="n">
         <v>0.0359</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="1" t="n">
         <v>0.0281</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" s="1" t="n">
         <v>0.0334</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="n">
         <v>29403</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="1" t="n">
         <v>0.0053</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" s="1" t="n">
         <v>0.0704</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="1" t="n">
         <v>0.0352</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" s="1" t="n">
         <v>0.098</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="n">
         <v>29434</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" s="1" t="n">
         <v>0.0064</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117" s="1" t="n">
         <v>0.0239</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="1" t="n">
         <v>0.021</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="1" t="n">
         <v>0.028</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="n">
         <v>29465</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" s="1" t="n">
         <v>0.0294</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="1" t="n">
         <v>-0.0061</v>
       </c>
-      <c r="E118" t="n">
-        <v>0.04219999999999999</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="E118" s="1" t="n">
+        <v>0.0422</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="n">
         <v>29495</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" s="1" t="n">
         <v>0.0095</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" s="1" t="n">
         <v>0.0199</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="1" t="n">
         <v>-0.0031</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" s="1" t="n">
         <v>0.0226</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="n">
         <v>29526</v>
       </c>
-      <c r="B120" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="C120" t="n">
+      <c r="B120" s="1" t="n">
+        <v>0.0096</v>
+      </c>
+      <c r="C120" s="1" t="n">
         <v>0.1056</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="1" t="n">
         <v>0.0441</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="1" t="n">
         <v>0.116</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="n">
         <v>29556</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" s="1" t="n">
         <v>0.0131</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="1" t="n">
         <v>-0.0315</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="1" t="n">
         <v>-0.0071</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" s="1" t="n">
         <v>-0.0252</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="n">
         <v>29587</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="1" t="n">
         <v>0.0104</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" s="1" t="n">
         <v>-0.0402</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" s="1" t="n">
         <v>-0.0566</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="n">
         <v>29618</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" s="1" t="n">
         <v>0.0107</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="1" t="n">
         <v>0.0162</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" s="1" t="n">
         <v>0.0244</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="n">
         <v>29646</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" s="1" t="n">
         <v>0.0121</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124" s="1" t="n">
         <v>0.0488</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="1" t="n">
         <v>0.0582</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" s="1" t="n">
         <v>0.0446</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="n">
         <v>29677</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" s="1" t="n">
         <v>0.0108</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" s="1" t="n">
         <v>-0.0108</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="1" t="n">
         <v>0.0145</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" s="1" t="n">
         <v>-0.0182</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="n">
         <v>29707</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="1" t="n">
         <v>0.0115</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126" s="1" t="n">
         <v>0.0128</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="1" t="n">
         <v>0.0285</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" s="1" t="n">
         <v>0.0129</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="n">
         <v>29738</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="1" t="n">
         <v>0.0135</v>
       </c>
-      <c r="C127" t="n">
-        <v>-0.009900000000000001</v>
-      </c>
-      <c r="D127" t="n">
+      <c r="C127" s="1" t="n">
+        <v>-0.0099</v>
+      </c>
+      <c r="D127" s="1" t="n">
         <v>0.0031</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" s="1" t="n">
         <v>-0.0349</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="4" t="n">
         <v>29768</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="1" t="n">
         <v>0.0124</v>
       </c>
-      <c r="C128" t="n">
+      <c r="C128" s="1" t="n">
         <v>-0.0031</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="1" t="n">
         <v>-0.0116</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128" s="1" t="n">
         <v>0.0077</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="n">
         <v>29799</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="1" t="n">
         <v>0.0128</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C129" s="1" t="n">
         <v>-0.0574</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="1" t="n">
         <v>-0.0294</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" s="1" t="n">
         <v>-0.0723</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="n">
         <v>29830</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="1" t="n">
         <v>0.0124</v>
       </c>
-      <c r="C130" t="n">
+      <c r="C130" s="1" t="n">
         <v>-0.0595</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="1" t="n">
         <v>-0.0198</v>
       </c>
-      <c r="E130" t="n">
-        <v>-0.06809999999999999</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="E130" s="1" t="n">
+        <v>-0.0681</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="n">
         <v>29860</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="1" t="n">
         <v>0.0121</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C131" s="1" t="n">
         <v>0.0613</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="1" t="n">
         <v>0.0466</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" s="1" t="n">
         <v>0.0834</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="4" t="n">
         <v>29891</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="1" t="n">
         <v>0.0107</v>
       </c>
-      <c r="C132" t="n">
+      <c r="C132" s="1" t="n">
         <v>0.0447</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="1" t="n">
         <v>0.0424</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E132" s="1" t="n">
         <v>0.0377</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="4" t="n">
         <v>29921</v>
       </c>
-      <c r="B133" t="n">
-        <v>0.008699999999999999</v>
-      </c>
-      <c r="C133" t="n">
+      <c r="B133" s="1" t="n">
+        <v>0.0087</v>
+      </c>
+      <c r="C133" s="1" t="n">
         <v>-0.0276</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="1" t="n">
         <v>-0.0227</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" s="1" t="n">
         <v>-0.0301</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="4" t="n">
         <v>29952</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134" s="1" t="n">
         <v>-0.0243</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" s="1" t="n">
         <v>-0.0229</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="4" t="n">
         <v>29983</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="1" t="n">
         <v>0.0092</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135" s="1" t="n">
         <v>-0.0494</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="1" t="n">
         <v>-0.0169</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" s="1" t="n">
         <v>-0.0738</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="4" t="n">
         <v>30011</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="1" t="n">
         <v>0.0098</v>
       </c>
-      <c r="C136" t="n">
-        <v>-0.008400000000000001</v>
-      </c>
-      <c r="D136" t="n">
+      <c r="C136" s="1" t="n">
+        <v>-0.0084</v>
+      </c>
+      <c r="D136" s="1" t="n">
         <v>0.0183</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" s="1" t="n">
         <v>-0.0192</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="4" t="n">
         <v>30042</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="1" t="n">
         <v>0.0113</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C137" s="1" t="n">
         <v>0.0437</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" s="1" t="n">
         <v>0.0247</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E137" s="1" t="n">
         <v>0.0584</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="4" t="n">
         <v>30072</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="1" t="n">
         <v>0.0106</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C138" s="1" t="n">
         <v>-0.0287</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" s="1" t="n">
         <v>-0.0195</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" s="1" t="n">
         <v>-0.0352</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="4" t="n">
         <v>30103</v>
       </c>
-      <c r="B139" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="C139" t="n">
+      <c r="B139" s="1" t="n">
+        <v>0.0096</v>
+      </c>
+      <c r="C139" s="1" t="n">
         <v>-0.0212</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" s="1" t="n">
         <v>-0.0167</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" s="1" t="n">
         <v>-0.0263</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="4" t="n">
         <v>30133</v>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" s="1" t="n">
         <v>0.0105</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C140" s="1" t="n">
         <v>-0.0215</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" s="1" t="n">
         <v>-0.0178</v>
       </c>
-      <c r="E140" t="n">
-        <v>-0.009300000000000001</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="E140" s="1" t="n">
+        <v>-0.0093</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="4" t="n">
         <v>30164</v>
       </c>
-      <c r="B141" t="n">
+      <c r="B141" s="1" t="n">
         <v>0.0076</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C141" s="1" t="n">
         <v>0.1199</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" s="1" t="n">
         <v>0.1091</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="4" t="n">
         <v>30195</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B142" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C142" s="1" t="n">
         <v>0.0182</v>
       </c>
-      <c r="D142" t="n">
-        <v>0.006500000000000001</v>
-      </c>
-      <c r="E142" t="n">
+      <c r="D142" s="1" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="E142" s="1" t="n">
         <v>0.0203</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="4" t="n">
         <v>30225</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B143" s="1" t="n">
         <v>0.0059</v>
       </c>
-      <c r="C143" t="n">
+      <c r="C143" s="1" t="n">
         <v>0.1189</v>
       </c>
-      <c r="D143" t="n">
-        <v>0.09949999999999999</v>
-      </c>
-      <c r="E143" t="n">
+      <c r="D143" s="1" t="n">
+        <v>0.0995</v>
+      </c>
+      <c r="E143" s="1" t="n">
         <v>0.1323</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="4" t="n">
         <v>30256</v>
       </c>
-      <c r="B144" t="n">
+      <c r="B144" s="1" t="n">
         <v>0.0063</v>
       </c>
-      <c r="C144" t="n">
+      <c r="C144" s="1" t="n">
         <v>0.0531</v>
       </c>
-      <c r="D144" t="n">
-        <v>0.04679999999999999</v>
-      </c>
-      <c r="E144" t="n">
+      <c r="D144" s="1" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="E144" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="4" t="n">
         <v>30286</v>
       </c>
-      <c r="B145" t="n">
+      <c r="B145" s="1" t="n">
         <v>0.0067</v>
       </c>
-      <c r="C145" t="n">
+      <c r="C145" s="1" t="n">
         <v>0.0123</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" s="1" t="n">
         <v>0.0148</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" s="1" t="n">
         <v>0.0117</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="4" t="n">
         <v>30317</v>
       </c>
-      <c r="B146" t="n">
+      <c r="B146" s="1" t="n">
         <v>0.0069</v>
       </c>
-      <c r="C146" t="n">
+      <c r="C146" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="1" t="n">
         <v>0.0581</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" s="1" t="n">
         <v>0.0371</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="4" t="n">
         <v>30348</v>
       </c>
-      <c r="B147" t="n">
+      <c r="B147" s="1" t="n">
         <v>0.0062</v>
       </c>
-      <c r="C147" t="n">
+      <c r="C147" s="1" t="n">
         <v>0.0321</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" s="1" t="n">
         <v>0.0286</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" s="1" t="n">
         <v>0.0373</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="4" t="n">
         <v>30376</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B148" s="1" t="n">
         <v>0.0063</v>
       </c>
-      <c r="C148" t="n">
+      <c r="C148" s="1" t="n">
         <v>0.0344</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="1" t="n">
         <v>0.0342</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="4" t="n">
         <v>30407</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B149" s="1" t="n">
         <v>0.0071</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C149" s="1" t="n">
         <v>0.0737</v>
       </c>
-      <c r="D149" t="n">
-        <v>0.07200000000000001</v>
-      </c>
-      <c r="E149" t="n">
+      <c r="D149" s="1" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="E149" s="1" t="n">
         <v>0.0604</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="4" t="n">
         <v>30437</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B150" s="1" t="n">
         <v>0.0069</v>
       </c>
-      <c r="C150" t="n">
+      <c r="C150" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" s="1" t="n">
         <v>0.0112</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="4" t="n">
         <v>30468</v>
       </c>
-      <c r="B151" t="n">
+      <c r="B151" s="1" t="n">
         <v>0.0067</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C151" s="1" t="n">
         <v>0.0374</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" s="1" t="n">
         <v>0.0535</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="4" t="n">
         <v>30498</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B152" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="C152" t="n">
-        <v>-0.03319999999999999</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-0.008100000000000001</v>
-      </c>
-      <c r="E152" t="n">
+      <c r="C152" s="1" t="n">
+        <v>-0.0332</v>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="E152" s="1" t="n">
         <v>-0.053</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="4" t="n">
         <v>30529</v>
       </c>
-      <c r="B153" t="n">
+      <c r="B153" s="1" t="n">
         <v>0.0076</v>
       </c>
-      <c r="C153" t="n">
+      <c r="C153" s="1" t="n">
         <v>0.0026</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="1" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" s="1" t="n">
         <v>-0.0189</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4" t="n">
         <v>30560</v>
       </c>
-      <c r="B154" t="n">
+      <c r="B154" s="1" t="n">
         <v>0.0076</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C154" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="1" t="n">
         <v>0.0121</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" s="1" t="n">
         <v>0.0217</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="4" t="n">
         <v>30590</v>
       </c>
-      <c r="B155" t="n">
+      <c r="B155" s="1" t="n">
         <v>0.0076</v>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" s="1" t="n">
         <v>-0.0267</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="1" t="n">
         <v>-0.0062</v>
       </c>
-      <c r="E155" t="n">
-        <v>-0.04389999999999999</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="E155" s="1" t="n">
+        <v>-0.0439</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="4" t="n">
         <v>30621</v>
       </c>
-      <c r="B156" t="n">
+      <c r="B156" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="C156" t="n">
+      <c r="C156" s="1" t="n">
         <v>0.0287</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" s="1" t="n">
         <v>0.0221</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" s="1" t="n">
         <v>0.0317</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="4" t="n">
         <v>30651</v>
       </c>
-      <c r="B157" t="n">
+      <c r="B157" s="1" t="n">
         <v>0.0073</v>
       </c>
-      <c r="C157" t="n">
+      <c r="C157" s="1" t="n">
         <v>-0.0104</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="1" t="n">
         <v>-0.006</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" s="1" t="n">
         <v>-0.0113</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="4" t="n">
         <v>30682</v>
       </c>
-      <c r="B158" t="n">
+      <c r="B158" s="1" t="n">
         <v>0.0076</v>
       </c>
-      <c r="C158" t="n">
+      <c r="C158" s="1" t="n">
         <v>-0.0116</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="1" t="n">
         <v>0.0325</v>
       </c>
-      <c r="E158" t="n">
-        <v>-0.05139999999999999</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="E158" s="1" t="n">
+        <v>-0.0514</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="4" t="n">
         <v>30713</v>
       </c>
-      <c r="B159" t="n">
+      <c r="B159" s="1" t="n">
         <v>0.0071</v>
       </c>
-      <c r="C159" t="n">
+      <c r="C159" s="1" t="n">
         <v>-0.0406</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="1" t="n">
         <v>-0.0163</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" s="1" t="n">
         <v>-0.051</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="4" t="n">
         <v>30742</v>
       </c>
-      <c r="B160" t="n">
+      <c r="B160" s="1" t="n">
         <v>0.0073</v>
       </c>
-      <c r="C160" t="n">
+      <c r="C160" s="1" t="n">
         <v>0.0138</v>
       </c>
-      <c r="D160" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="E160" t="n">
+      <c r="D160" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E160" s="1" t="n">
         <v>0.014</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="n">
         <v>30773</v>
       </c>
-      <c r="B161" t="n">
+      <c r="B161" s="1" t="n">
         <v>0.0081</v>
       </c>
-      <c r="C161" t="n">
-        <v>0.002999999999999999</v>
-      </c>
-      <c r="D161" t="n">
+      <c r="C161" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D161" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="E161" t="n">
+      <c r="E161" s="1" t="n">
         <v>0.002</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="4" t="n">
         <v>30803</v>
       </c>
-      <c r="B162" t="n">
+      <c r="B162" s="1" t="n">
         <v>0.0078</v>
       </c>
-      <c r="C162" t="n">
+      <c r="C162" s="1" t="n">
         <v>-0.052</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" s="1" t="n">
         <v>-0.0576</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E162" s="1" t="n">
         <v>-0.05</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="4" t="n">
         <v>30834</v>
       </c>
-      <c r="B163" t="n">
+      <c r="B163" s="1" t="n">
         <v>0.0075</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C163" s="1" t="n">
         <v>0.0256</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="1" t="n">
         <v>0.0236</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163" s="1" t="n">
         <v>0.0444</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="4" t="n">
         <v>30864</v>
       </c>
-      <c r="B164" t="n">
-        <v>0.008200000000000001</v>
-      </c>
-      <c r="C164" t="n">
+      <c r="B164" s="1" t="n">
+        <v>0.0082</v>
+      </c>
+      <c r="C164" s="1" t="n">
         <v>-0.019</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" s="1" t="n">
         <v>-0.0253</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E164" s="1" t="n">
         <v>-0.0185</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="4" t="n">
         <v>30895</v>
       </c>
-      <c r="B165" t="n">
+      <c r="B165" s="1" t="n">
         <v>0.0083</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C165" s="1" t="n">
         <v>0.111</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165" s="1" t="n">
         <v>0.1137</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E165" s="1" t="n">
         <v>0.1155</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="4" t="n">
         <v>30926</v>
       </c>
-      <c r="B166" t="n">
+      <c r="B166" s="1" t="n">
         <v>0.0086</v>
       </c>
-      <c r="C166" t="n">
-        <v>0.0005999999999999998</v>
-      </c>
-      <c r="D166" t="n">
+      <c r="C166" s="1" t="n">
+        <v>0.0006</v>
+      </c>
+      <c r="D166" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E166" s="1" t="n">
         <v>-0.024</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="4" t="n">
         <v>30956</v>
       </c>
-      <c r="B167" t="n">
+      <c r="B167" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="C167" t="n">
-        <v>0.001600000000000001</v>
-      </c>
-      <c r="D167" t="n">
+      <c r="C167" s="1" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="D167" s="1" t="n">
         <v>-0.0043</v>
       </c>
-      <c r="E167" t="n">
+      <c r="E167" s="1" t="n">
         <v>0.0017</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="4" t="n">
         <v>30987</v>
       </c>
-      <c r="B168" t="n">
+      <c r="B168" s="1" t="n">
         <v>0.0073</v>
       </c>
-      <c r="C168" t="n">
+      <c r="C168" s="1" t="n">
         <v>-0.0104</v>
       </c>
-      <c r="D168" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="E168" t="n">
+      <c r="D168" s="1" t="n">
+        <v>0.0084</v>
+      </c>
+      <c r="E168" s="1" t="n">
         <v>-0.0264</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="4" t="n">
         <v>31017</v>
       </c>
-      <c r="B169" t="n">
+      <c r="B169" s="1" t="n">
         <v>0.0064</v>
       </c>
-      <c r="C169" t="n">
+      <c r="C169" s="1" t="n">
         <v>0.0249</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169" s="1" t="n">
         <v>0.0225</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E169" s="1" t="n">
         <v>0.0258</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="4" t="n">
         <v>31048</v>
       </c>
-      <c r="B170" t="n">
+      <c r="B170" s="1" t="n">
         <v>0.0065</v>
       </c>
-      <c r="C170" t="n">
+      <c r="C170" s="1" t="n">
         <v>0.0862</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170" s="1" t="n">
         <v>0.0601</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E170" s="1" t="n">
         <v>0.1096</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="4" t="n">
         <v>31079</v>
       </c>
-      <c r="B171" t="n">
+      <c r="B171" s="1" t="n">
         <v>0.0058</v>
       </c>
-      <c r="C171" t="n">
+      <c r="C171" s="1" t="n">
         <v>0.018</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171" s="1" t="n">
         <v>0.0213</v>
       </c>
-      <c r="E171" t="n">
+      <c r="E171" s="1" t="n">
         <v>0.0161</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="4" t="n">
         <v>31107</v>
       </c>
-      <c r="B172" t="n">
+      <c r="B172" s="1" t="n">
         <v>0.0062</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C172" s="1" t="n">
         <v>-0.0021</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172" s="1" t="n">
         <v>0.0207</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E172" s="1" t="n">
         <v>-0.0166</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="n">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="4" t="n">
         <v>31138</v>
       </c>
-      <c r="B173" t="n">
+      <c r="B173" s="1" t="n">
         <v>0.0072</v>
       </c>
-      <c r="C173" t="n">
-        <v>-0.002399999999999999</v>
-      </c>
-      <c r="D173" t="n">
+      <c r="C173" s="1" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="D173" s="1" t="n">
         <v>0.0185</v>
       </c>
-      <c r="E173" t="n">
+      <c r="E173" s="1" t="n">
         <v>-0.0184</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="4" t="n">
         <v>31168</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B174" s="1" t="n">
         <v>0.0066</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C174" s="1" t="n">
         <v>0.0573</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" s="1" t="n">
         <v>0.0495</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E174" s="1" t="n">
         <v>0.0578</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="n">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="4" t="n">
         <v>31199</v>
       </c>
-      <c r="B175" t="n">
+      <c r="B175" s="1" t="n">
         <v>0.0055</v>
       </c>
-      <c r="C175" t="n">
+      <c r="C175" s="1" t="n">
         <v>0.0182</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E175" s="1" t="n">
         <v>0.0148</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="4" t="n">
         <v>31229</v>
       </c>
-      <c r="B176" t="n">
+      <c r="B176" s="1" t="n">
         <v>0.0062</v>
       </c>
-      <c r="C176" t="n">
+      <c r="C176" s="1" t="n">
         <v>-0.001</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176" s="1" t="n">
         <v>-0.0119</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E176" s="1" t="n">
         <v>0.0061</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="4" t="n">
         <v>31260</v>
       </c>
-      <c r="B177" t="n">
+      <c r="B177" s="1" t="n">
         <v>0.0055</v>
       </c>
-      <c r="C177" t="n">
+      <c r="C177" s="1" t="n">
         <v>-0.0046</v>
       </c>
-      <c r="D177" t="n">
-        <v>0.007800000000000001</v>
-      </c>
-      <c r="E177" t="n">
+      <c r="D177" s="1" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="E177" s="1" t="n">
         <v>-0.0163</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="4" t="n">
         <v>31291</v>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="C178" t="n">
+      <c r="C178" s="1" t="n">
         <v>-0.0391</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" s="1" t="n">
         <v>-0.0438</v>
       </c>
-      <c r="E178" t="n">
+      <c r="E178" s="1" t="n">
         <v>-0.0434</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="4" t="n">
         <v>31321</v>
       </c>
-      <c r="B179" t="n">
+      <c r="B179" s="1" t="n">
         <v>0.0065</v>
       </c>
-      <c r="C179" t="n">
+      <c r="C179" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="D179" t="n">
+      <c r="D179" s="1" t="n">
         <v>0.053</v>
       </c>
-      <c r="E179" t="n">
+      <c r="E179" s="1" t="n">
         <v>0.0396</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="4" t="n">
         <v>31352</v>
       </c>
-      <c r="B180" t="n">
+      <c r="B180" s="1" t="n">
         <v>0.0061</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C180" s="1" t="n">
         <v>0.0707</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D180" s="1" t="n">
         <v>0.0486</v>
       </c>
-      <c r="E180" t="n">
-        <v>0.08869999999999999</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="E180" s="1" t="n">
+        <v>0.0887</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="4" t="n">
         <v>31382</v>
       </c>
-      <c r="B181" t="n">
+      <c r="B181" s="1" t="n">
         <v>0.0065</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C181" s="1" t="n">
         <v>0.0453</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181" s="1" t="n">
         <v>0.0433</v>
       </c>
-      <c r="E181" t="n">
+      <c r="E181" s="1" t="n">
         <v>0.0559</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="4" t="n">
         <v>31413</v>
       </c>
-      <c r="B182" t="n">
+      <c r="B182" s="1" t="n">
         <v>0.0056</v>
       </c>
-      <c r="C182" t="n">
+      <c r="C182" s="1" t="n">
         <v>0.0121</v>
       </c>
-      <c r="D182" t="n">
+      <c r="D182" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="E182" t="n">
+      <c r="E182" s="1" t="n">
         <v>0.0101</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="4" t="n">
         <v>31444</v>
       </c>
-      <c r="B183" t="n">
+      <c r="B183" s="1" t="n">
         <v>0.0053</v>
       </c>
-      <c r="C183" t="n">
+      <c r="C183" s="1" t="n">
         <v>0.0767</v>
       </c>
-      <c r="D183" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="E183" t="n">
+      <c r="D183" s="1" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="E183" s="1" t="n">
         <v>0.0786</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="4" t="n">
         <v>31472</v>
       </c>
-      <c r="B184" t="n">
+      <c r="B184" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="C184" t="n">
+      <c r="C184" s="1" t="n">
         <v>0.0551</v>
       </c>
-      <c r="D184" t="n">
+      <c r="D184" s="1" t="n">
         <v>0.0453</v>
       </c>
-      <c r="E184" t="n">
+      <c r="E184" s="1" t="n">
         <v>0.0602</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="4" t="n">
         <v>31503</v>
       </c>
-      <c r="B185" t="n">
+      <c r="B185" s="1" t="n">
         <v>0.0052</v>
       </c>
-      <c r="C185" t="n">
-        <v>-0.007600000000000001</v>
-      </c>
-      <c r="D185" t="n">
+      <c r="C185" s="1" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="D185" s="1" t="n">
         <v>-0.0284</v>
       </c>
-      <c r="E185" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="E185" s="1" t="n">
+        <v>0.0085</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="4" t="n">
         <v>31533</v>
       </c>
-      <c r="B186" t="n">
+      <c r="B186" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="C186" t="n">
+      <c r="C186" s="1" t="n">
         <v>0.0511</v>
       </c>
-      <c r="D186" t="n">
+      <c r="D186" s="1" t="n">
         <v>0.0487</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E186" s="1" t="n">
         <v>0.051</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="4" t="n">
         <v>31564</v>
       </c>
-      <c r="B187" t="n">
+      <c r="B187" s="1" t="n">
         <v>0.0052</v>
       </c>
-      <c r="C187" t="n">
+      <c r="C187" s="1" t="n">
         <v>0.0158</v>
       </c>
-      <c r="D187" t="n">
+      <c r="D187" s="1" t="n">
         <v>0.0245</v>
       </c>
-      <c r="E187" t="n">
+      <c r="E187" s="1" t="n">
         <v>0.0166</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="4" t="n">
         <v>31594</v>
       </c>
-      <c r="B188" t="n">
+      <c r="B188" s="1" t="n">
         <v>0.0052</v>
       </c>
-      <c r="C188" t="n">
+      <c r="C188" s="1" t="n">
         <v>-0.0591</v>
       </c>
-      <c r="D188" t="n">
+      <c r="D188" s="1" t="n">
         <v>-0.0295</v>
       </c>
-      <c r="E188" t="n">
+      <c r="E188" s="1" t="n">
         <v>-0.0767</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="4" t="n">
         <v>31625</v>
       </c>
-      <c r="B189" t="n">
+      <c r="B189" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C189" t="n">
+      <c r="C189" s="1" t="n">
         <v>0.0653</v>
       </c>
-      <c r="D189" t="n">
-        <v>0.08960000000000001</v>
-      </c>
-      <c r="E189" t="n">
+      <c r="D189" s="1" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="E189" s="1" t="n">
         <v>0.0429</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="4" t="n">
         <v>31656</v>
       </c>
-      <c r="B190" t="n">
+      <c r="B190" s="1" t="n">
         <v>0.0045</v>
       </c>
-      <c r="C190" t="n">
+      <c r="C190" s="1" t="n">
         <v>-0.0814</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190" s="1" t="n">
         <v>-0.0692</v>
       </c>
-      <c r="E190" t="n">
+      <c r="E190" s="1" t="n">
         <v>-0.099</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="4" t="n">
         <v>31686</v>
       </c>
-      <c r="B191" t="n">
+      <c r="B191" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C191" t="n">
+      <c r="C191" s="1" t="n">
         <v>0.051</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191" s="1" t="n">
         <v>0.051</v>
       </c>
-      <c r="E191" t="n">
+      <c r="E191" s="1" t="n">
         <v>0.0549</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="4" t="n">
         <v>31717</v>
       </c>
-      <c r="B192" t="n">
+      <c r="B192" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C192" t="n">
+      <c r="C192" s="1" t="n">
         <v>0.0156</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192" s="1" t="n">
         <v>0.0144</v>
       </c>
-      <c r="E192" t="n">
+      <c r="E192" s="1" t="n">
         <v>0.0181</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="4" t="n">
         <v>31747</v>
       </c>
-      <c r="B193" t="n">
+      <c r="B193" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="C193" t="n">
+      <c r="C193" s="1" t="n">
         <v>-0.0277</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193" s="1" t="n">
         <v>-0.0281</v>
       </c>
-      <c r="E193" t="n">
+      <c r="E193" s="1" t="n">
         <v>-0.0254</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="4" t="n">
         <v>31778</v>
       </c>
-      <c r="B194" t="n">
+      <c r="B194" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C194" t="n">
+      <c r="C194" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="D194" t="n">
+      <c r="D194" s="1" t="n">
         <v>0.1087</v>
       </c>
-      <c r="E194" t="n">
+      <c r="E194" s="1" t="n">
         <v>0.1385</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="4" t="n">
         <v>31809</v>
       </c>
-      <c r="B195" t="n">
+      <c r="B195" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C195" t="n">
+      <c r="C195" s="1" t="n">
         <v>0.0481</v>
       </c>
-      <c r="D195" t="n">
+      <c r="D195" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="E195" t="n">
-        <v>0.07679999999999999</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="E195" s="1" t="n">
+        <v>0.0768</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="4" t="n">
         <v>31837</v>
       </c>
-      <c r="B196" t="n">
+      <c r="B196" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C196" t="n">
+      <c r="C196" s="1" t="n">
         <v>0.021</v>
       </c>
-      <c r="D196" t="n">
+      <c r="D196" s="1" t="n">
         <v>0.0269</v>
       </c>
-      <c r="E196" t="n">
+      <c r="E196" s="1" t="n">
         <v>0.0159</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="4" t="n">
         <v>31868</v>
       </c>
-      <c r="B197" t="n">
+      <c r="B197" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C197" t="n">
+      <c r="C197" s="1" t="n">
         <v>-0.0165</v>
       </c>
-      <c r="D197" t="n">
+      <c r="D197" s="1" t="n">
         <v>-0.017</v>
       </c>
-      <c r="E197" t="n">
+      <c r="E197" s="1" t="n">
         <v>-0.0183</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="4" t="n">
         <v>31898</v>
       </c>
-      <c r="B198" t="n">
+      <c r="B198" s="1" t="n">
         <v>0.0038</v>
       </c>
-      <c r="C198" t="n">
+      <c r="C198" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="D198" t="n">
+      <c r="D198" s="1" t="n">
         <v>0.0071</v>
       </c>
-      <c r="E198" t="n">
+      <c r="E198" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="4" t="n">
         <v>31929</v>
       </c>
-      <c r="B199" t="n">
+      <c r="B199" s="1" t="n">
         <v>0.0048</v>
       </c>
-      <c r="C199" t="n">
+      <c r="C199" s="1" t="n">
         <v>0.0439</v>
       </c>
-      <c r="D199" t="n">
-        <v>0.04559999999999999</v>
-      </c>
-      <c r="E199" t="n">
+      <c r="D199" s="1" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="E199" s="1" t="n">
         <v>0.0429</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="4" t="n">
         <v>31959</v>
       </c>
-      <c r="B200" t="n">
+      <c r="B200" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C200" t="n">
+      <c r="C200" s="1" t="n">
         <v>0.043</v>
       </c>
-      <c r="D200" t="n">
+      <c r="D200" s="1" t="n">
         <v>0.0396</v>
       </c>
-      <c r="E200" t="n">
+      <c r="E200" s="1" t="n">
         <v>0.0507</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="4" t="n">
         <v>31990</v>
       </c>
-      <c r="B201" t="n">
+      <c r="B201" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C201" t="n">
+      <c r="C201" s="1" t="n">
         <v>0.0399</v>
       </c>
-      <c r="D201" t="n">
+      <c r="D201" s="1" t="n">
         <v>0.0273</v>
       </c>
-      <c r="E201" t="n">
+      <c r="E201" s="1" t="n">
         <v>0.0451</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="n">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="4" t="n">
         <v>32021</v>
       </c>
-      <c r="B202" t="n">
+      <c r="B202" s="1" t="n">
         <v>0.0045</v>
       </c>
-      <c r="C202" t="n">
+      <c r="C202" s="1" t="n">
         <v>-0.0213</v>
       </c>
-      <c r="D202" t="n">
+      <c r="D202" s="1" t="n">
         <v>-0.0242</v>
       </c>
-      <c r="E202" t="n">
+      <c r="E202" s="1" t="n">
         <v>-0.0204</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="n">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="4" t="n">
         <v>32051</v>
       </c>
-      <c r="B203" t="n">
+      <c r="B203" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="C203" t="n">
+      <c r="C203" s="1" t="n">
         <v>-0.2259</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D203" s="1" t="n">
         <v>-0.203</v>
       </c>
-      <c r="E203" t="n">
+      <c r="E203" s="1" t="n">
         <v>-0.2423</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="n">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="4" t="n">
         <v>32082</v>
       </c>
-      <c r="B204" t="n">
+      <c r="B204" s="1" t="n">
         <v>0.0035</v>
       </c>
-      <c r="C204" t="n">
+      <c r="C204" s="1" t="n">
         <v>-0.0741</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D204" s="1" t="n">
         <v>-0.055</v>
       </c>
-      <c r="E204" t="n">
-        <v>-0.08529999999999999</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="E204" s="1" t="n">
+        <v>-0.0853</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="4" t="n">
         <v>32112</v>
       </c>
-      <c r="B205" t="n">
+      <c r="B205" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C205" t="n">
+      <c r="C205" s="1" t="n">
         <v>0.0721</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D205" s="1" t="n">
         <v>0.049</v>
       </c>
-      <c r="E205" t="n">
-        <v>0.09140000000000001</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="E205" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="4" t="n">
         <v>32143</v>
       </c>
-      <c r="B206" t="n">
+      <c r="B206" s="1" t="n">
         <v>0.0029</v>
       </c>
-      <c r="C206" t="n">
+      <c r="C206" s="1" t="n">
         <v>0.045</v>
       </c>
-      <c r="D206" t="n">
-        <v>0.07730000000000001</v>
-      </c>
-      <c r="E206" t="n">
+      <c r="D206" s="1" t="n">
+        <v>0.0773</v>
+      </c>
+      <c r="E206" s="1" t="n">
         <v>0.0204</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="n">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="4" t="n">
         <v>32174</v>
       </c>
-      <c r="B207" t="n">
+      <c r="B207" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C207" t="n">
+      <c r="C207" s="1" t="n">
         <v>0.0523</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207" s="1" t="n">
         <v>0.0396</v>
       </c>
-      <c r="E207" t="n">
+      <c r="E207" s="1" t="n">
         <v>0.0576</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="n">
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="4" t="n">
         <v>32203</v>
       </c>
-      <c r="B208" t="n">
+      <c r="B208" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C208" t="n">
+      <c r="C208" s="1" t="n">
         <v>-0.0182</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208" s="1" t="n">
         <v>-0.0062</v>
       </c>
-      <c r="E208" t="n">
+      <c r="E208" s="1" t="n">
         <v>-0.024</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="4" t="n">
         <v>32234</v>
       </c>
-      <c r="B209" t="n">
+      <c r="B209" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C209" t="n">
+      <c r="C209" s="1" t="n">
         <v>0.0103</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209" s="1" t="n">
         <v>0.0155</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E209" s="1" t="n">
         <v>-0.0044</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="n">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="4" t="n">
         <v>32264</v>
       </c>
-      <c r="B210" t="n">
+      <c r="B210" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="C210" t="n">
+      <c r="C210" s="1" t="n">
         <v>0.0024</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="E210" t="n">
+      <c r="E210" s="1" t="n">
         <v>-0.0033</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="4" t="n">
         <v>32295</v>
       </c>
-      <c r="B211" t="n">
+      <c r="B211" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="C211" t="n">
+      <c r="C211" s="1" t="n">
         <v>0.0527</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211" s="1" t="n">
         <v>0.0417</v>
       </c>
-      <c r="E211" t="n">
+      <c r="E211" s="1" t="n">
         <v>0.0525</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="4" t="n">
         <v>32325</v>
       </c>
-      <c r="B212" t="n">
+      <c r="B212" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="C212" t="n">
+      <c r="C212" s="1" t="n">
         <v>-0.0074</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212" s="1" t="n">
         <v>0.0023</v>
       </c>
-      <c r="E212" t="n">
+      <c r="E212" s="1" t="n">
         <v>-0.0169</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="4" t="n">
         <v>32356</v>
       </c>
-      <c r="B213" t="n">
+      <c r="B213" s="1" t="n">
         <v>0.0059</v>
       </c>
-      <c r="C213" t="n">
+      <c r="C213" s="1" t="n">
         <v>-0.0272</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213" s="1" t="n">
         <v>-0.0142</v>
       </c>
-      <c r="E213" t="n">
+      <c r="E213" s="1" t="n">
         <v>-0.0308</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="4" t="n">
         <v>32387</v>
       </c>
-      <c r="B214" t="n">
+      <c r="B214" s="1" t="n">
         <v>0.0062</v>
       </c>
-      <c r="C214" t="n">
-        <v>0.03929999999999999</v>
-      </c>
-      <c r="D214" t="n">
+      <c r="C214" s="1" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="D214" s="1" t="n">
         <v>0.0349</v>
       </c>
-      <c r="E214" t="n">
+      <c r="E214" s="1" t="n">
         <v>0.0483</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="4" t="n">
         <v>32417</v>
       </c>
-      <c r="B215" t="n">
+      <c r="B215" s="1" t="n">
         <v>0.0061</v>
       </c>
-      <c r="C215" t="n">
+      <c r="C215" s="1" t="n">
         <v>0.0177</v>
       </c>
-      <c r="D215" t="n">
+      <c r="D215" s="1" t="n">
         <v>0.0264</v>
       </c>
-      <c r="E215" t="n">
+      <c r="E215" s="1" t="n">
         <v>0.0117</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="4" t="n">
         <v>32448</v>
       </c>
-      <c r="B216" t="n">
+      <c r="B216" s="1" t="n">
         <v>0.0057</v>
       </c>
-      <c r="C216" t="n">
+      <c r="C216" s="1" t="n">
         <v>-0.017</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D216" s="1" t="n">
         <v>-0.0066</v>
       </c>
-      <c r="E216" t="n">
+      <c r="E216" s="1" t="n">
         <v>-0.0215</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="4" t="n">
         <v>32478</v>
       </c>
-      <c r="B217" t="n">
+      <c r="B217" s="1" t="n">
         <v>0.0063</v>
       </c>
-      <c r="C217" t="n">
+      <c r="C217" s="1" t="n">
         <v>0.0211</v>
       </c>
-      <c r="D217" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-      <c r="E217" t="n">
+      <c r="D217" s="1" t="n">
+        <v>0.0088</v>
+      </c>
+      <c r="E217" s="1" t="n">
         <v>0.0299</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="4" t="n">
         <v>32509</v>
       </c>
-      <c r="B218" t="n">
+      <c r="B218" s="1" t="n">
         <v>0.0055</v>
       </c>
-      <c r="C218" t="n">
-        <v>0.06619999999999999</v>
-      </c>
-      <c r="D218" t="n">
+      <c r="C218" s="1" t="n">
+        <v>0.0662</v>
+      </c>
+      <c r="D218" s="1" t="n">
         <v>0.0684</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E218" s="1" t="n">
         <v>0.0668</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="4" t="n">
         <v>32540</v>
       </c>
-      <c r="B219" t="n">
+      <c r="B219" s="1" t="n">
         <v>0.0061</v>
       </c>
-      <c r="C219" t="n">
+      <c r="C219" s="1" t="n">
         <v>-0.0162</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D219" s="1" t="n">
         <v>-0.0097</v>
       </c>
-      <c r="E219" t="n">
+      <c r="E219" s="1" t="n">
         <v>-0.0218</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="4" t="n">
         <v>32568</v>
       </c>
-      <c r="B220" t="n">
+      <c r="B220" s="1" t="n">
         <v>0.0067</v>
       </c>
-      <c r="C220" t="n">
+      <c r="C220" s="1" t="n">
         <v>0.0224</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D220" s="1" t="n">
         <v>0.0271</v>
       </c>
-      <c r="E220" t="n">
+      <c r="E220" s="1" t="n">
         <v>0.0249</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="4" t="n">
         <v>32599</v>
       </c>
-      <c r="B221" t="n">
+      <c r="B221" s="1" t="n">
         <v>0.0067</v>
       </c>
-      <c r="C221" t="n">
-        <v>0.05019999999999999</v>
-      </c>
-      <c r="D221" t="n">
+      <c r="C221" s="1" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="D221" s="1" t="n">
         <v>0.0403</v>
       </c>
-      <c r="E221" t="n">
+      <c r="E221" s="1" t="n">
         <v>0.0593</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="4" t="n">
         <v>32629</v>
       </c>
-      <c r="B222" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="C222" t="n">
+      <c r="B222" s="1" t="n">
+        <v>0.0079</v>
+      </c>
+      <c r="C222" s="1" t="n">
         <v>0.0407</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D222" s="1" t="n">
         <v>0.0392</v>
       </c>
-      <c r="E222" t="n">
+      <c r="E222" s="1" t="n">
         <v>0.0483</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="4" t="n">
         <v>32660</v>
       </c>
-      <c r="B223" t="n">
+      <c r="B223" s="1" t="n">
         <v>0.0071</v>
       </c>
-      <c r="C223" t="n">
-        <v>-0.006199999999999999</v>
-      </c>
-      <c r="D223" t="n">
+      <c r="C223" s="1" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="D223" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="E223" t="n">
+      <c r="E223" s="1" t="n">
         <v>-0.0122</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="4" t="n">
         <v>32690</v>
       </c>
-      <c r="B224" t="n">
+      <c r="B224" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="C224" t="n">
-        <v>0.07880000000000001</v>
-      </c>
-      <c r="D224" t="n">
-        <v>0.05860000000000001</v>
-      </c>
-      <c r="E224" t="n">
+      <c r="C224" s="1" t="n">
+        <v>0.0788</v>
+      </c>
+      <c r="D224" s="1" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="E224" s="1" t="n">
         <v>0.1007</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="4" t="n">
         <v>32721</v>
       </c>
-      <c r="B225" t="n">
+      <c r="B225" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="C225" t="n">
+      <c r="C225" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="D225" t="n">
+      <c r="D225" s="1" t="n">
         <v>0.0248</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E225" s="1" t="n">
         <v>0.0128</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="4" t="n">
         <v>32752</v>
       </c>
-      <c r="B226" t="n">
+      <c r="B226" s="1" t="n">
         <v>0.0065</v>
       </c>
-      <c r="C226" t="n">
+      <c r="C226" s="1" t="n">
         <v>-0.0011</v>
       </c>
-      <c r="D226" t="n">
+      <c r="D226" s="1" t="n">
         <v>0.0004</v>
       </c>
-      <c r="E226" t="n">
+      <c r="E226" s="1" t="n">
         <v>0.0058</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="4" t="n">
         <v>32782</v>
       </c>
-      <c r="B227" t="n">
+      <c r="B227" s="1" t="n">
         <v>0.0068</v>
       </c>
-      <c r="C227" t="n">
+      <c r="C227" s="1" t="n">
         <v>-0.0297</v>
       </c>
-      <c r="D227" t="n">
+      <c r="D227" s="1" t="n">
         <v>-0.0271</v>
       </c>
-      <c r="E227" t="n">
+      <c r="E227" s="1" t="n">
         <v>-0.0171</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="4" t="n">
         <v>32813</v>
       </c>
-      <c r="B228" t="n">
+      <c r="B228" s="1" t="n">
         <v>0.0069</v>
       </c>
-      <c r="C228" t="n">
+      <c r="C228" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="D228" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="E228" t="n">
+      <c r="D228" s="1" t="n">
+        <v>0.0079</v>
+      </c>
+      <c r="E228" s="1" t="n">
         <v>0.0217</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="4" t="n">
         <v>32843</v>
       </c>
-      <c r="B229" t="n">
+      <c r="B229" s="1" t="n">
         <v>0.0061</v>
       </c>
-      <c r="C229" t="n">
+      <c r="C229" s="1" t="n">
         <v>0.0179</v>
       </c>
-      <c r="D229" t="n">
+      <c r="D229" s="1" t="n">
         <v>0.0219</v>
       </c>
-      <c r="E229" t="n">
+      <c r="E229" s="1" t="n">
         <v>0.0153</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="4" t="n">
         <v>32874</v>
       </c>
-      <c r="B230" t="n">
+      <c r="B230" s="1" t="n">
         <v>0.0057</v>
       </c>
-      <c r="C230" t="n">
+      <c r="C230" s="1" t="n">
         <v>-0.0723</v>
       </c>
-      <c r="D230" t="n">
-        <v>-0.07339999999999999</v>
-      </c>
-      <c r="E230" t="n">
+      <c r="D230" s="1" t="n">
+        <v>-0.0734</v>
+      </c>
+      <c r="E230" s="1" t="n">
         <v>-0.0771</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="4" t="n">
         <v>32905</v>
       </c>
-      <c r="B231" t="n">
+      <c r="B231" s="1" t="n">
         <v>0.0057</v>
       </c>
-      <c r="C231" t="n">
+      <c r="C231" s="1" t="n">
         <v>0.0169</v>
       </c>
-      <c r="D231" t="n">
+      <c r="D231" s="1" t="n">
         <v>0.0258</v>
       </c>
-      <c r="E231" t="n">
-        <v>0.006500000000000001</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="E231" s="1" t="n">
+        <v>0.0065</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="4" t="n">
         <v>32933</v>
       </c>
-      <c r="B232" t="n">
+      <c r="B232" s="1" t="n">
         <v>0.0064</v>
       </c>
-      <c r="C232" t="n">
+      <c r="C232" s="1" t="n">
         <v>0.0247</v>
       </c>
-      <c r="D232" t="n">
+      <c r="D232" s="1" t="n">
         <v>0.0058</v>
       </c>
-      <c r="E232" t="n">
+      <c r="E232" s="1" t="n">
         <v>0.0414</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="n">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="4" t="n">
         <v>32964</v>
       </c>
-      <c r="B233" t="n">
+      <c r="B233" s="1" t="n">
         <v>0.0069</v>
       </c>
-      <c r="C233" t="n">
+      <c r="C233" s="1" t="n">
         <v>-0.0267</v>
       </c>
-      <c r="D233" t="n">
-        <v>-0.04480000000000001</v>
-      </c>
-      <c r="E233" t="n">
+      <c r="D233" s="1" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="E233" s="1" t="n">
         <v>-0.0114</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="4" t="n">
         <v>32994</v>
       </c>
-      <c r="B234" t="n">
+      <c r="B234" s="1" t="n">
         <v>0.0068</v>
       </c>
-      <c r="C234" t="n">
+      <c r="C234" s="1" t="n">
         <v>0.0911</v>
       </c>
-      <c r="D234" t="n">
-        <v>0.07049999999999999</v>
-      </c>
-      <c r="E234" t="n">
+      <c r="D234" s="1" t="n">
+        <v>0.0705</v>
+      </c>
+      <c r="E234" s="1" t="n">
         <v>0.1063</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="4" t="n">
         <v>33025</v>
       </c>
-      <c r="B235" t="n">
+      <c r="B235" s="1" t="n">
         <v>0.0063</v>
       </c>
-      <c r="C235" t="n">
+      <c r="C235" s="1" t="n">
         <v>-0.0046</v>
       </c>
-      <c r="D235" t="n">
+      <c r="D235" s="1" t="n">
         <v>-0.0141</v>
       </c>
-      <c r="E235" t="n">
+      <c r="E235" s="1" t="n">
         <v>0.0127</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="4" t="n">
         <v>33055</v>
       </c>
-      <c r="B236" t="n">
+      <c r="B236" s="1" t="n">
         <v>0.0068</v>
       </c>
-      <c r="C236" t="n">
+      <c r="C236" s="1" t="n">
         <v>-0.0122</v>
       </c>
-      <c r="D236" t="n">
+      <c r="D236" s="1" t="n">
         <v>-0.0212</v>
       </c>
-      <c r="E236" t="n">
+      <c r="E236" s="1" t="n">
         <v>-0.016</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="4" t="n">
         <v>33086</v>
       </c>
-      <c r="B237" t="n">
+      <c r="B237" s="1" t="n">
         <v>0.0066</v>
       </c>
-      <c r="C237" t="n">
+      <c r="C237" s="1" t="n">
         <v>-0.0946</v>
       </c>
-      <c r="D237" t="n">
+      <c r="D237" s="1" t="n">
         <v>-0.1017</v>
       </c>
-      <c r="E237" t="n">
+      <c r="E237" s="1" t="n">
         <v>-0.1011</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="4" t="n">
         <v>33117</v>
       </c>
-      <c r="B238" t="n">
+      <c r="B238" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="C238" t="n">
+      <c r="C238" s="1" t="n">
         <v>-0.0551</v>
       </c>
-      <c r="D238" t="n">
+      <c r="D238" s="1" t="n">
         <v>-0.0668</v>
       </c>
-      <c r="E238" t="n">
+      <c r="E238" s="1" t="n">
         <v>-0.0612</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="4" t="n">
         <v>33147</v>
       </c>
-      <c r="B239" t="n">
+      <c r="B239" s="1" t="n">
         <v>0.0068</v>
       </c>
-      <c r="C239" t="n">
+      <c r="C239" s="1" t="n">
         <v>-0.0124</v>
       </c>
-      <c r="D239" t="n">
+      <c r="D239" s="1" t="n">
         <v>-0.003</v>
       </c>
-      <c r="E239" t="n">
+      <c r="E239" s="1" t="n">
         <v>-0.001</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="4" t="n">
         <v>33178</v>
       </c>
-      <c r="B240" t="n">
+      <c r="B240" s="1" t="n">
         <v>0.0057</v>
       </c>
-      <c r="C240" t="n">
+      <c r="C240" s="1" t="n">
         <v>0.0692</v>
       </c>
-      <c r="D240" t="n">
+      <c r="D240" s="1" t="n">
         <v>0.0512</v>
       </c>
-      <c r="E240" t="n">
+      <c r="E240" s="1" t="n">
         <v>0.0747</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="4" t="n">
         <v>33208</v>
       </c>
-      <c r="B241" t="n">
+      <c r="B241" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="C241" t="n">
+      <c r="C241" s="1" t="n">
         <v>0.0306</v>
       </c>
-      <c r="D241" t="n">
+      <c r="D241" s="1" t="n">
         <v>0.0204</v>
       </c>
-      <c r="E241" t="n">
+      <c r="E241" s="1" t="n">
         <v>0.0379</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="n">
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="4" t="n">
         <v>33239</v>
       </c>
-      <c r="B242" t="n">
+      <c r="B242" s="1" t="n">
         <v>0.0052</v>
       </c>
-      <c r="C242" t="n">
-        <v>0.05209999999999999</v>
-      </c>
-      <c r="D242" t="n">
+      <c r="C242" s="1" t="n">
+        <v>0.0521</v>
+      </c>
+      <c r="D242" s="1" t="n">
         <v>0.0503</v>
       </c>
-      <c r="E242" t="n">
+      <c r="E242" s="1" t="n">
         <v>0.0645</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="n">
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="4" t="n">
         <v>33270</v>
       </c>
-      <c r="B243" t="n">
+      <c r="B243" s="1" t="n">
         <v>0.0048</v>
       </c>
-      <c r="C243" t="n">
+      <c r="C243" s="1" t="n">
         <v>0.0767</v>
       </c>
-      <c r="D243" t="n">
-        <v>0.07730000000000001</v>
-      </c>
-      <c r="E243" t="n">
+      <c r="D243" s="1" t="n">
+        <v>0.0773</v>
+      </c>
+      <c r="E243" s="1" t="n">
         <v>0.0818</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="n">
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="4" t="n">
         <v>33298</v>
       </c>
-      <c r="B244" t="n">
+      <c r="B244" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C244" t="n">
+      <c r="C244" s="1" t="n">
         <v>0.031</v>
       </c>
-      <c r="D244" t="n">
+      <c r="D244" s="1" t="n">
         <v>0.0322</v>
       </c>
-      <c r="E244" t="n">
+      <c r="E244" s="1" t="n">
         <v>0.0438</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="n">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="4" t="n">
         <v>33329</v>
       </c>
-      <c r="B245" t="n">
+      <c r="B245" s="1" t="n">
         <v>0.0053</v>
       </c>
-      <c r="C245" t="n">
+      <c r="C245" s="1" t="n">
         <v>0.0025</v>
       </c>
-      <c r="D245" t="n">
-        <v>0.005500000000000001</v>
-      </c>
-      <c r="E245" t="n">
+      <c r="D245" s="1" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="E245" s="1" t="n">
         <v>-0.0036</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="n">
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="4" t="n">
         <v>33359</v>
       </c>
-      <c r="B246" t="n">
+      <c r="B246" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C246" t="n">
+      <c r="C246" s="1" t="n">
         <v>0.0413</v>
       </c>
-      <c r="D246" t="n">
+      <c r="D246" s="1" t="n">
         <v>0.0489</v>
       </c>
-      <c r="E246" t="n">
+      <c r="E246" s="1" t="n">
         <v>0.0472</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="n">
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="4" t="n">
         <v>33390</v>
       </c>
-      <c r="B247" t="n">
+      <c r="B247" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C247" t="n">
+      <c r="C247" s="1" t="n">
         <v>-0.0452</v>
       </c>
-      <c r="D247" t="n">
+      <c r="D247" s="1" t="n">
         <v>-0.0383</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E247" s="1" t="n">
         <v>-0.0496</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="n">
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="4" t="n">
         <v>33420</v>
       </c>
-      <c r="B248" t="n">
+      <c r="B248" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="C248" t="n">
+      <c r="C248" s="1" t="n">
         <v>0.0473</v>
       </c>
-      <c r="D248" t="n">
+      <c r="D248" s="1" t="n">
         <v>0.0391</v>
       </c>
-      <c r="E248" t="n">
+      <c r="E248" s="1" t="n">
         <v>0.0532</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="n">
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="4" t="n">
         <v>33451</v>
       </c>
-      <c r="B249" t="n">
+      <c r="B249" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C249" t="n">
+      <c r="C249" s="1" t="n">
         <v>0.0278</v>
       </c>
-      <c r="D249" t="n">
+      <c r="D249" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="E249" t="n">
+      <c r="E249" s="1" t="n">
         <v>0.0344</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="n">
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="4" t="n">
         <v>33482</v>
       </c>
-      <c r="B250" t="n">
+      <c r="B250" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C250" t="n">
+      <c r="C250" s="1" t="n">
         <v>-0.0113</v>
       </c>
-      <c r="D250" t="n">
+      <c r="D250" s="1" t="n">
         <v>-0.0183</v>
       </c>
-      <c r="E250" t="n">
+      <c r="E250" s="1" t="n">
         <v>-0.0193</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="n">
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="4" t="n">
         <v>33512</v>
       </c>
-      <c r="B251" t="n">
+      <c r="B251" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C251" t="n">
+      <c r="C251" s="1" t="n">
         <v>0.0171</v>
       </c>
-      <c r="D251" t="n">
+      <c r="D251" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="E251" t="n">
+      <c r="E251" s="1" t="n">
         <v>0.0161</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="4" t="n">
         <v>33543</v>
       </c>
-      <c r="B252" t="n">
+      <c r="B252" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C252" t="n">
+      <c r="C252" s="1" t="n">
         <v>-0.0381</v>
       </c>
-      <c r="D252" t="n">
+      <c r="D252" s="1" t="n">
         <v>-0.0552</v>
       </c>
-      <c r="E252" t="n">
+      <c r="E252" s="1" t="n">
         <v>-0.027</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="n">
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="4" t="n">
         <v>33573</v>
       </c>
-      <c r="B253" t="n">
+      <c r="B253" s="1" t="n">
         <v>0.0038</v>
       </c>
-      <c r="C253" t="n">
+      <c r="C253" s="1" t="n">
         <v>0.1123</v>
       </c>
-      <c r="D253" t="n">
+      <c r="D253" s="1" t="n">
         <v>0.0868</v>
       </c>
-      <c r="E253" t="n">
+      <c r="E253" s="1" t="n">
         <v>0.1418</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="n">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="4" t="n">
         <v>33604</v>
       </c>
-      <c r="B254" t="n">
+      <c r="B254" s="1" t="n">
         <v>0.0034</v>
       </c>
-      <c r="C254" t="n">
+      <c r="C254" s="1" t="n">
         <v>-0.0025</v>
       </c>
-      <c r="D254" t="n">
+      <c r="D254" s="1" t="n">
         <v>0.0525</v>
       </c>
-      <c r="E254" t="n">
+      <c r="E254" s="1" t="n">
         <v>-0.0164</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="n">
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="4" t="n">
         <v>33635</v>
       </c>
-      <c r="B255" t="n">
+      <c r="B255" s="1" t="n">
         <v>0.0028</v>
       </c>
-      <c r="C255" t="n">
+      <c r="C255" s="1" t="n">
         <v>0.0136</v>
       </c>
-      <c r="D255" t="n">
+      <c r="D255" s="1" t="n">
         <v>0.0697</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255" s="1" t="n">
         <v>0.0036</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="n">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="4" t="n">
         <v>33664</v>
       </c>
-      <c r="B256" t="n">
+      <c r="B256" s="1" t="n">
         <v>0.0034</v>
       </c>
-      <c r="C256" t="n">
+      <c r="C256" s="1" t="n">
         <v>-0.0231</v>
       </c>
-      <c r="D256" t="n">
+      <c r="D256" s="1" t="n">
         <v>-0.0108</v>
       </c>
-      <c r="E256" t="n">
+      <c r="E256" s="1" t="n">
         <v>-0.0303</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="n">
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="4" t="n">
         <v>33695</v>
       </c>
-      <c r="B257" t="n">
+      <c r="B257" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="C257" t="n">
+      <c r="C257" s="1" t="n">
         <v>0.0141</v>
       </c>
-      <c r="D257" t="n">
+      <c r="D257" s="1" t="n">
         <v>0.031</v>
       </c>
-      <c r="E257" t="n">
+      <c r="E257" s="1" t="n">
         <v>-0.0026</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="n">
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="4" t="n">
         <v>33725</v>
       </c>
-      <c r="B258" t="n">
+      <c r="B258" s="1" t="n">
         <v>0.0028</v>
       </c>
-      <c r="C258" t="n">
+      <c r="C258" s="1" t="n">
         <v>0.0058</v>
       </c>
-      <c r="D258" t="n">
+      <c r="D258" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="E258" t="n">
-        <v>0.008100000000000001</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="E258" s="1" t="n">
+        <v>0.0081</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="4" t="n">
         <v>33756</v>
       </c>
-      <c r="B259" t="n">
+      <c r="B259" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="C259" t="n">
+      <c r="C259" s="1" t="n">
         <v>-0.0201</v>
       </c>
-      <c r="D259" t="n">
+      <c r="D259" s="1" t="n">
         <v>0.0002</v>
       </c>
-      <c r="E259" t="n">
+      <c r="E259" s="1" t="n">
         <v>-0.027</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="n">
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="4" t="n">
         <v>33786</v>
       </c>
-      <c r="B260" t="n">
+      <c r="B260" s="1" t="n">
         <v>0.0031</v>
       </c>
-      <c r="C260" t="n">
+      <c r="C260" s="1" t="n">
         <v>0.0409</v>
       </c>
-      <c r="D260" t="n">
+      <c r="D260" s="1" t="n">
         <v>0.0246</v>
       </c>
-      <c r="E260" t="n">
+      <c r="E260" s="1" t="n">
         <v>0.0418</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="n">
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="4" t="n">
         <v>33817</v>
       </c>
-      <c r="B261" t="n">
+      <c r="B261" s="1" t="n">
         <v>0.0026</v>
       </c>
-      <c r="C261" t="n">
+      <c r="C261" s="1" t="n">
         <v>-0.0212</v>
       </c>
-      <c r="D261" t="n">
-        <v>-0.04480000000000001</v>
-      </c>
-      <c r="E261" t="n">
+      <c r="D261" s="1" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="E261" s="1" t="n">
         <v>-0.0139</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="n">
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="4" t="n">
         <v>33848</v>
       </c>
-      <c r="B262" t="n">
+      <c r="B262" s="1" t="n">
         <v>0.0026</v>
       </c>
-      <c r="C262" t="n">
+      <c r="C262" s="1" t="n">
         <v>0.0145</v>
       </c>
-      <c r="D262" t="n">
+      <c r="D262" s="1" t="n">
         <v>0.0118</v>
       </c>
-      <c r="E262" t="n">
+      <c r="E262" s="1" t="n">
         <v>0.0167</v>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="n">
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="4" t="n">
         <v>33878</v>
       </c>
-      <c r="B263" t="n">
+      <c r="B263" s="1" t="n">
         <v>0.0023</v>
       </c>
-      <c r="C263" t="n">
+      <c r="C263" s="1" t="n">
         <v>0.0125</v>
       </c>
-      <c r="D263" t="n">
+      <c r="D263" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="E263" t="n">
+      <c r="E263" s="1" t="n">
         <v>0.0258</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="n">
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="4" t="n">
         <v>33909</v>
       </c>
-      <c r="B264" t="n">
+      <c r="B264" s="1" t="n">
         <v>0.0023</v>
       </c>
-      <c r="C264" t="n">
+      <c r="C264" s="1" t="n">
         <v>0.0437</v>
       </c>
-      <c r="D264" t="n">
+      <c r="D264" s="1" t="n">
         <v>0.0495</v>
       </c>
-      <c r="E264" t="n">
+      <c r="E264" s="1" t="n">
         <v>0.0498</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="n">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="4" t="n">
         <v>33939</v>
       </c>
-      <c r="B265" t="n">
+      <c r="B265" s="1" t="n">
         <v>0.0028</v>
       </c>
-      <c r="C265" t="n">
+      <c r="C265" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="D265" t="n">
+      <c r="D265" s="1" t="n">
         <v>0.0377</v>
       </c>
-      <c r="E265" t="n">
+      <c r="E265" s="1" t="n">
         <v>0.0086</v>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="2" t="n">
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="4" t="n">
         <v>33970</v>
       </c>
-      <c r="B266" t="n">
+      <c r="B266" s="1" t="n">
         <v>0.0023</v>
       </c>
-      <c r="C266" t="n">
+      <c r="C266" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="D266" t="n">
+      <c r="D266" s="1" t="n">
         <v>0.0563</v>
       </c>
-      <c r="E266" t="n">
-        <v>-0.009000000000000001</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="E266" s="1" t="n">
+        <v>-0.009</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="4" t="n">
         <v>34001</v>
       </c>
-      <c r="B267" t="n">
+      <c r="B267" s="1" t="n">
         <v>0.0022</v>
       </c>
-      <c r="C267" t="n">
+      <c r="C267" s="1" t="n">
         <v>0.0034</v>
       </c>
-      <c r="D267" t="n">
+      <c r="D267" s="1" t="n">
         <v>0.0271</v>
       </c>
-      <c r="E267" t="n">
+      <c r="E267" s="1" t="n">
         <v>-0.027</v>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="n">
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="4" t="n">
         <v>34029</v>
       </c>
-      <c r="B268" t="n">
+      <c r="B268" s="1" t="n">
         <v>0.0025</v>
       </c>
-      <c r="C268" t="n">
+      <c r="C268" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="D268" t="n">
+      <c r="D268" s="1" t="n">
         <v>0.0293</v>
       </c>
-      <c r="E268" t="n">
+      <c r="E268" s="1" t="n">
         <v>0.018</v>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="n">
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="4" t="n">
         <v>34060</v>
       </c>
-      <c r="B269" t="n">
+      <c r="B269" s="1" t="n">
         <v>0.0024</v>
       </c>
-      <c r="C269" t="n">
+      <c r="C269" s="1" t="n">
         <v>-0.0281</v>
       </c>
-      <c r="D269" t="n">
+      <c r="D269" s="1" t="n">
         <v>-0.0132</v>
       </c>
-      <c r="E269" t="n">
+      <c r="E269" s="1" t="n">
         <v>-0.0492</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="2" t="n">
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="4" t="n">
         <v>34090</v>
       </c>
-      <c r="B270" t="n">
+      <c r="B270" s="1" t="n">
         <v>0.0022</v>
       </c>
-      <c r="C270" t="n">
+      <c r="C270" s="1" t="n">
         <v>0.0311</v>
       </c>
-      <c r="D270" t="n">
+      <c r="D270" s="1" t="n">
         <v>0.0113</v>
       </c>
-      <c r="E270" t="n">
+      <c r="E270" s="1" t="n">
         <v>0.0424</v>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="2" t="n">
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="4" t="n">
         <v>34121</v>
       </c>
-      <c r="B271" t="n">
+      <c r="B271" s="1" t="n">
         <v>0.0025</v>
       </c>
-      <c r="C271" t="n">
+      <c r="C271" s="1" t="n">
         <v>0.0055</v>
       </c>
-      <c r="D271" t="n">
+      <c r="D271" s="1" t="n">
         <v>0.031</v>
       </c>
-      <c r="E271" t="n">
+      <c r="E271" s="1" t="n">
         <v>-0.0089</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="2" t="n">
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="4" t="n">
         <v>34151</v>
       </c>
-      <c r="B272" t="n">
+      <c r="B272" s="1" t="n">
         <v>0.0024</v>
       </c>
-      <c r="C272" t="n">
+      <c r="C272" s="1" t="n">
         <v>-0.001</v>
       </c>
-      <c r="D272" t="n">
+      <c r="D272" s="1" t="n">
         <v>0.0138</v>
       </c>
-      <c r="E272" t="n">
+      <c r="E272" s="1" t="n">
         <v>-0.0185</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="2" t="n">
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="4" t="n">
         <v>34182</v>
       </c>
-      <c r="B273" t="n">
+      <c r="B273" s="1" t="n">
         <v>0.0025</v>
       </c>
-      <c r="C273" t="n">
+      <c r="C273" s="1" t="n">
         <v>0.0397</v>
       </c>
-      <c r="D273" t="n">
+      <c r="D273" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="E273" t="n">
+      <c r="E273" s="1" t="n">
         <v>0.0354</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="2" t="n">
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="4" t="n">
         <v>34213</v>
       </c>
-      <c r="B274" t="n">
+      <c r="B274" s="1" t="n">
         <v>0.0026</v>
       </c>
-      <c r="C274" t="n">
+      <c r="C274" s="1" t="n">
         <v>0.0014</v>
       </c>
-      <c r="D274" t="n">
+      <c r="D274" s="1" t="n">
         <v>-0.0008</v>
       </c>
-      <c r="E274" t="n">
+      <c r="E274" s="1" t="n">
         <v>-0.0051</v>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="2" t="n">
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="4" t="n">
         <v>34243</v>
       </c>
-      <c r="B275" t="n">
+      <c r="B275" s="1" t="n">
         <v>0.0022</v>
       </c>
-      <c r="C275" t="n">
+      <c r="C275" s="1" t="n">
         <v>0.0164</v>
       </c>
-      <c r="D275" t="n">
+      <c r="D275" s="1" t="n">
         <v>-0.0029</v>
       </c>
-      <c r="E275" t="n">
+      <c r="E275" s="1" t="n">
         <v>0.0333</v>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="n">
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="4" t="n">
         <v>34274</v>
       </c>
-      <c r="B276" t="n">
+      <c r="B276" s="1" t="n">
         <v>0.0025</v>
       </c>
-      <c r="C276" t="n">
+      <c r="C276" s="1" t="n">
         <v>-0.0162</v>
       </c>
-      <c r="D276" t="n">
+      <c r="D276" s="1" t="n">
         <v>-0.0218</v>
       </c>
-      <c r="E276" t="n">
+      <c r="E276" s="1" t="n">
         <v>-0.0022</v>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="2" t="n">
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="4" t="n">
         <v>34304</v>
       </c>
-      <c r="B277" t="n">
+      <c r="B277" s="1" t="n">
         <v>0.0023</v>
       </c>
-      <c r="C277" t="n">
+      <c r="C277" s="1" t="n">
         <v>0.0188</v>
       </c>
-      <c r="D277" t="n">
+      <c r="D277" s="1" t="n">
         <v>0.0227</v>
       </c>
-      <c r="E277" t="n">
+      <c r="E277" s="1" t="n">
         <v>0.0157</v>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="2" t="n">
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="4" t="n">
         <v>34335</v>
       </c>
-      <c r="B278" t="n">
+      <c r="B278" s="1" t="n">
         <v>0.0025</v>
       </c>
-      <c r="C278" t="n">
+      <c r="C278" s="1" t="n">
         <v>0.0312</v>
       </c>
-      <c r="D278" t="n">
+      <c r="D278" s="1" t="n">
         <v>0.0229</v>
       </c>
-      <c r="E278" t="n">
+      <c r="E278" s="1" t="n">
         <v>0.0238</v>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="2" t="n">
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="4" t="n">
         <v>34366</v>
       </c>
-      <c r="B279" t="n">
+      <c r="B279" s="1" t="n">
         <v>0.0021</v>
       </c>
-      <c r="C279" t="n">
+      <c r="C279" s="1" t="n">
         <v>-0.0234</v>
       </c>
-      <c r="D279" t="n">
+      <c r="D279" s="1" t="n">
         <v>-0.0393</v>
       </c>
-      <c r="E279" t="n">
+      <c r="E279" s="1" t="n">
         <v>-0.0169</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="2" t="n">
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="4" t="n">
         <v>34394</v>
       </c>
-      <c r="B280" t="n">
+      <c r="B280" s="1" t="n">
         <v>0.0027</v>
       </c>
-      <c r="C280" t="n">
+      <c r="C280" s="1" t="n">
         <v>-0.0452</v>
       </c>
-      <c r="D280" t="n">
+      <c r="D280" s="1" t="n">
         <v>-0.0353</v>
       </c>
-      <c r="E280" t="n">
-        <v>-0.04849999999999999</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="E280" s="1" t="n">
+        <v>-0.0485</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="4" t="n">
         <v>34425</v>
       </c>
-      <c r="B281" t="n">
+      <c r="B281" s="1" t="n">
         <v>0.0027</v>
       </c>
-      <c r="C281" t="n">
+      <c r="C281" s="1" t="n">
         <v>0.0095</v>
       </c>
-      <c r="D281" t="n">
+      <c r="D281" s="1" t="n">
         <v>0.0157</v>
       </c>
-      <c r="E281" t="n">
-        <v>0.004500000000000001</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="E281" s="1" t="n">
+        <v>0.0045</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="4" t="n">
         <v>34455</v>
       </c>
-      <c r="B282" t="n">
+      <c r="B282" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="C282" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="D282" t="n">
+      <c r="C282" s="1" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="D282" s="1" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="E282" t="n">
+      <c r="E282" s="1" t="n">
         <v>0.0105</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="2" t="n">
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="4" t="n">
         <v>34486</v>
       </c>
-      <c r="B283" t="n">
+      <c r="B283" s="1" t="n">
         <v>0.0031</v>
       </c>
-      <c r="C283" t="n">
+      <c r="C283" s="1" t="n">
         <v>-0.0273</v>
       </c>
-      <c r="D283" t="n">
+      <c r="D283" s="1" t="n">
         <v>-0.0245</v>
       </c>
-      <c r="E283" t="n">
+      <c r="E283" s="1" t="n">
         <v>-0.0327</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="2" t="n">
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="4" t="n">
         <v>34516</v>
       </c>
-      <c r="B284" t="n">
+      <c r="B284" s="1" t="n">
         <v>0.0028</v>
       </c>
-      <c r="C284" t="n">
+      <c r="C284" s="1" t="n">
         <v>0.031</v>
       </c>
-      <c r="D284" t="n">
+      <c r="D284" s="1" t="n">
         <v>0.0318</v>
       </c>
-      <c r="E284" t="n">
+      <c r="E284" s="1" t="n">
         <v>0.0279</v>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="2" t="n">
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="4" t="n">
         <v>34547</v>
       </c>
-      <c r="B285" t="n">
+      <c r="B285" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C285" t="n">
+      <c r="C285" s="1" t="n">
         <v>0.0439</v>
       </c>
-      <c r="D285" t="n">
-        <v>0.03759999999999999</v>
-      </c>
-      <c r="E285" t="n">
+      <c r="D285" s="1" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="E285" s="1" t="n">
         <v>0.0539</v>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="2" t="n">
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="4" t="n">
         <v>34578</v>
       </c>
-      <c r="B286" t="n">
+      <c r="B286" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C286" t="n">
+      <c r="C286" s="1" t="n">
         <v>-0.0191</v>
       </c>
-      <c r="D286" t="n">
+      <c r="D286" s="1" t="n">
         <v>-0.0343</v>
       </c>
-      <c r="E286" t="n">
+      <c r="E286" s="1" t="n">
         <v>-0.0124</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="2" t="n">
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="4" t="n">
         <v>34608</v>
       </c>
-      <c r="B287" t="n">
+      <c r="B287" s="1" t="n">
         <v>0.0038</v>
       </c>
-      <c r="C287" t="n">
+      <c r="C287" s="1" t="n">
         <v>0.0173</v>
       </c>
-      <c r="D287" t="n">
+      <c r="D287" s="1" t="n">
         <v>0.0018</v>
       </c>
-      <c r="E287" t="n">
+      <c r="E287" s="1" t="n">
         <v>0.0188</v>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" s="2" t="n">
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="4" t="n">
         <v>34639</v>
       </c>
-      <c r="B288" t="n">
+      <c r="B288" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C288" t="n">
+      <c r="C288" s="1" t="n">
         <v>-0.0366</v>
       </c>
-      <c r="D288" t="n">
+      <c r="D288" s="1" t="n">
         <v>-0.0466</v>
       </c>
-      <c r="E288" t="n">
+      <c r="E288" s="1" t="n">
         <v>-0.0327</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" s="2" t="n">
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="4" t="n">
         <v>34669</v>
       </c>
-      <c r="B289" t="n">
+      <c r="B289" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C289" t="n">
+      <c r="C289" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="D289" t="n">
+      <c r="D289" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="E289" t="n">
+      <c r="E289" s="1" t="n">
         <v>0.0148</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="2" t="n">
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="4" t="n">
         <v>34700</v>
       </c>
-      <c r="B290" t="n">
+      <c r="B290" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C290" t="n">
+      <c r="C290" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="D290" t="n">
+      <c r="D290" s="1" t="n">
         <v>0.0415</v>
       </c>
-      <c r="E290" t="n">
+      <c r="E290" s="1" t="n">
         <v>0.0189</v>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" s="2" t="n">
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="4" t="n">
         <v>34731</v>
       </c>
-      <c r="B291" t="n">
+      <c r="B291" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C291" t="n">
+      <c r="C291" s="1" t="n">
         <v>0.0403</v>
       </c>
-      <c r="D291" t="n">
+      <c r="D291" s="1" t="n">
         <v>0.0507</v>
       </c>
-      <c r="E291" t="n">
+      <c r="E291" s="1" t="n">
         <v>0.0388</v>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" s="2" t="n">
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="4" t="n">
         <v>34759</v>
       </c>
-      <c r="B292" t="n">
+      <c r="B292" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C292" t="n">
+      <c r="C292" s="1" t="n">
         <v>0.0265</v>
       </c>
-      <c r="D292" t="n">
+      <c r="D292" s="1" t="n">
         <v>0.0061</v>
       </c>
-      <c r="E292" t="n">
+      <c r="E292" s="1" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" s="2" t="n">
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="4" t="n">
         <v>34790</v>
       </c>
-      <c r="B293" t="n">
+      <c r="B293" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C293" t="n">
+      <c r="C293" s="1" t="n">
         <v>0.0255</v>
       </c>
-      <c r="D293" t="n">
+      <c r="D293" s="1" t="n">
         <v>0.0343</v>
       </c>
-      <c r="E293" t="n">
+      <c r="E293" s="1" t="n">
         <v>0.0226</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" s="2" t="n">
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="4" t="n">
         <v>34820</v>
       </c>
-      <c r="B294" t="n">
+      <c r="B294" s="1" t="n">
         <v>0.0054</v>
       </c>
-      <c r="C294" t="n">
+      <c r="C294" s="1" t="n">
         <v>0.0344</v>
       </c>
-      <c r="D294" t="n">
+      <c r="D294" s="1" t="n">
         <v>0.0506</v>
       </c>
-      <c r="E294" t="n">
+      <c r="E294" s="1" t="n">
         <v>0.0307</v>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" s="2" t="n">
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="4" t="n">
         <v>34851</v>
       </c>
-      <c r="B295" t="n">
+      <c r="B295" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C295" t="n">
+      <c r="C295" s="1" t="n">
         <v>0.0319</v>
       </c>
-      <c r="D295" t="n">
+      <c r="D295" s="1" t="n">
         <v>0.023</v>
       </c>
-      <c r="E295" t="n">
+      <c r="E295" s="1" t="n">
         <v>0.0377</v>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" s="2" t="n">
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="4" t="n">
         <v>34881</v>
       </c>
-      <c r="B296" t="n">
+      <c r="B296" s="1" t="n">
         <v>0.0045</v>
       </c>
-      <c r="C296" t="n">
+      <c r="C296" s="1" t="n">
         <v>0.0416</v>
       </c>
-      <c r="D296" t="n">
+      <c r="D296" s="1" t="n">
         <v>0.0403</v>
       </c>
-      <c r="E296" t="n">
-        <v>0.04099999999999999</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="E296" s="1" t="n">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="4" t="n">
         <v>34912</v>
       </c>
-      <c r="B297" t="n">
+      <c r="B297" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C297" t="n">
+      <c r="C297" s="1" t="n">
         <v>0.0102</v>
       </c>
-      <c r="D297" t="n">
+      <c r="D297" s="1" t="n">
         <v>0.0373</v>
       </c>
-      <c r="E297" t="n">
+      <c r="E297" s="1" t="n">
         <v>0.0024</v>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" s="2" t="n">
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="4" t="n">
         <v>34943</v>
       </c>
-      <c r="B298" t="n">
+      <c r="B298" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C298" t="n">
+      <c r="C298" s="1" t="n">
         <v>0.0379</v>
       </c>
-      <c r="D298" t="n">
+      <c r="D298" s="1" t="n">
         <v>0.0434</v>
       </c>
-      <c r="E298" t="n">
+      <c r="E298" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" s="2" t="n">
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="4" t="n">
         <v>34973</v>
       </c>
-      <c r="B299" t="n">
+      <c r="B299" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C299" t="n">
+      <c r="C299" s="1" t="n">
         <v>-0.0104</v>
       </c>
-      <c r="D299" t="n">
+      <c r="D299" s="1" t="n">
         <v>-0.0267</v>
       </c>
-      <c r="E299" t="n">
+      <c r="E299" s="1" t="n">
         <v>-0.001</v>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" s="2" t="n">
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="4" t="n">
         <v>35004</v>
       </c>
-      <c r="B300" t="n">
+      <c r="B300" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C300" t="n">
-        <v>0.04380000000000001</v>
-      </c>
-      <c r="D300" t="n">
-        <v>0.05019999999999999</v>
-      </c>
-      <c r="E300" t="n">
+      <c r="C300" s="1" t="n">
+        <v>0.0438</v>
+      </c>
+      <c r="D300" s="1" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="E300" s="1" t="n">
         <v>0.0414</v>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" s="2" t="n">
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="4" t="n">
         <v>35034</v>
       </c>
-      <c r="B301" t="n">
+      <c r="B301" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="C301" t="n">
+      <c r="C301" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="D301" t="n">
+      <c r="D301" s="1" t="n">
         <v>0.0148</v>
       </c>
-      <c r="E301" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="E301" s="1" t="n">
+        <v>0.0099</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="4" t="n">
         <v>35065</v>
       </c>
-      <c r="B302" t="n">
+      <c r="B302" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C302" t="n">
+      <c r="C302" s="1" t="n">
         <v>0.0269</v>
       </c>
-      <c r="D302" t="n">
+      <c r="D302" s="1" t="n">
         <v>0.0273</v>
       </c>
-      <c r="E302" t="n">
+      <c r="E302" s="1" t="n">
         <v>0.0287</v>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" s="2" t="n">
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="4" t="n">
         <v>35096</v>
       </c>
-      <c r="B303" t="n">
+      <c r="B303" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C303" t="n">
+      <c r="C303" s="1" t="n">
         <v>0.0172</v>
       </c>
-      <c r="D303" t="n">
+      <c r="D303" s="1" t="n">
         <v>0.0185</v>
       </c>
-      <c r="E303" t="n">
+      <c r="E303" s="1" t="n">
         <v>0.0187</v>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" s="2" t="n">
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="4" t="n">
         <v>35125</v>
       </c>
-      <c r="B304" t="n">
+      <c r="B304" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C304" t="n">
+      <c r="C304" s="1" t="n">
         <v>0.0113</v>
       </c>
-      <c r="D304" t="n">
+      <c r="D304" s="1" t="n">
         <v>0.0131</v>
       </c>
-      <c r="E304" t="n">
+      <c r="E304" s="1" t="n">
         <v>0.0052</v>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" s="2" t="n">
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="4" t="n">
         <v>35156</v>
       </c>
-      <c r="B305" t="n">
+      <c r="B305" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C305" t="n">
+      <c r="C305" s="1" t="n">
         <v>0.0252</v>
       </c>
-      <c r="D305" t="n">
+      <c r="D305" s="1" t="n">
         <v>-0.0026</v>
       </c>
-      <c r="E305" t="n">
+      <c r="E305" s="1" t="n">
         <v>0.0291</v>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" s="2" t="n">
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="4" t="n">
         <v>35186</v>
       </c>
-      <c r="B306" t="n">
+      <c r="B306" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C306" t="n">
+      <c r="C306" s="1" t="n">
         <v>0.0278</v>
       </c>
-      <c r="D306" t="n">
+      <c r="D306" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="E306" t="n">
+      <c r="E306" s="1" t="n">
         <v>0.0361</v>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" s="2" t="n">
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="4" t="n">
         <v>35217</v>
       </c>
-      <c r="B307" t="n">
+      <c r="B307" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C307" t="n">
-        <v>-0.007299999999999999</v>
-      </c>
-      <c r="D307" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="E307" t="n">
+      <c r="C307" s="1" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="D307" s="1" t="n">
+        <v>0.0006</v>
+      </c>
+      <c r="E307" s="1" t="n">
         <v>-0.0038</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" s="2" t="n">
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="4" t="n">
         <v>35247</v>
       </c>
-      <c r="B308" t="n">
+      <c r="B308" s="1" t="n">
         <v>0.0045</v>
       </c>
-      <c r="C308" t="n">
+      <c r="C308" s="1" t="n">
         <v>-0.0551</v>
       </c>
-      <c r="D308" t="n">
+      <c r="D308" s="1" t="n">
         <v>-0.0408</v>
       </c>
-      <c r="E308" t="n">
-        <v>-0.06309999999999999</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="E308" s="1" t="n">
+        <v>-0.0631</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="4" t="n">
         <v>35278</v>
       </c>
-      <c r="B309" t="n">
+      <c r="B309" s="1" t="n">
         <v>0.0041</v>
       </c>
-      <c r="C309" t="n">
+      <c r="C309" s="1" t="n">
         <v>0.0318</v>
       </c>
-      <c r="D309" t="n">
+      <c r="D309" s="1" t="n">
         <v>0.0344</v>
       </c>
-      <c r="E309" t="n">
+      <c r="E309" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" s="2" t="n">
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="4" t="n">
         <v>35309</v>
       </c>
-      <c r="B310" t="n">
+      <c r="B310" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C310" t="n">
+      <c r="C310" s="1" t="n">
         <v>0.0545</v>
       </c>
-      <c r="D310" t="n">
+      <c r="D310" s="1" t="n">
         <v>0.0325</v>
       </c>
-      <c r="E310" t="n">
+      <c r="E310" s="1" t="n">
         <v>0.0659</v>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" s="2" t="n">
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="4" t="n">
         <v>35339</v>
       </c>
-      <c r="B311" t="n">
+      <c r="B311" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C311" t="n">
+      <c r="C311" s="1" t="n">
         <v>0.0129</v>
       </c>
-      <c r="D311" t="n">
+      <c r="D311" s="1" t="n">
         <v>0.0345</v>
       </c>
-      <c r="E311" t="n">
+      <c r="E311" s="1" t="n">
         <v>0.0028</v>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" s="2" t="n">
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="4" t="n">
         <v>35370</v>
       </c>
-      <c r="B312" t="n">
+      <c r="B312" s="1" t="n">
         <v>0.0041</v>
       </c>
-      <c r="C312" t="n">
-        <v>0.06660000000000001</v>
-      </c>
-      <c r="D312" t="n">
+      <c r="C312" s="1" t="n">
+        <v>0.0666</v>
+      </c>
+      <c r="D312" s="1" t="n">
         <v>0.0683</v>
       </c>
-      <c r="E312" t="n">
+      <c r="E312" s="1" t="n">
         <v>0.0677</v>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" s="2" t="n">
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="4" t="n">
         <v>35400</v>
       </c>
-      <c r="B313" t="n">
+      <c r="B313" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C313" t="n">
+      <c r="C313" s="1" t="n">
         <v>-0.0124</v>
       </c>
-      <c r="D313" t="n">
+      <c r="D313" s="1" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="E313" t="n">
+      <c r="E313" s="1" t="n">
         <v>-0.0153</v>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" s="2" t="n">
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="4" t="n">
         <v>35431</v>
       </c>
-      <c r="B314" t="n">
+      <c r="B314" s="1" t="n">
         <v>0.0045</v>
       </c>
-      <c r="C314" t="n">
+      <c r="C314" s="1" t="n">
         <v>0.0541</v>
       </c>
-      <c r="D314" t="n">
-        <v>0.04389999999999999</v>
-      </c>
-      <c r="E314" t="n">
-        <v>0.06269999999999999</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="D314" s="1" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="E314" s="1" t="n">
+        <v>0.0627</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="4" t="n">
         <v>35462</v>
       </c>
-      <c r="B315" t="n">
+      <c r="B315" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C315" t="n">
-        <v>-0.0008999999999999998</v>
-      </c>
-      <c r="D315" t="n">
+      <c r="C315" s="1" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="D315" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="E315" t="n">
-        <v>-0.004099999999999999</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="E315" s="1" t="n">
+        <v>-0.0041</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="4" t="n">
         <v>35490</v>
       </c>
-      <c r="B316" t="n">
+      <c r="B316" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C316" t="n">
+      <c r="C316" s="1" t="n">
         <v>-0.0459</v>
       </c>
-      <c r="D316" t="n">
+      <c r="D316" s="1" t="n">
         <v>-0.0447</v>
       </c>
-      <c r="E316" t="n">
+      <c r="E316" s="1" t="n">
         <v>-0.0556</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" s="2" t="n">
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="4" t="n">
         <v>35521</v>
       </c>
-      <c r="B317" t="n">
+      <c r="B317" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C317" t="n">
+      <c r="C317" s="1" t="n">
         <v>0.0447</v>
       </c>
-      <c r="D317" t="n">
+      <c r="D317" s="1" t="n">
         <v>0.0286</v>
       </c>
-      <c r="E317" t="n">
+      <c r="E317" s="1" t="n">
         <v>0.0592</v>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" s="2" t="n">
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="4" t="n">
         <v>35551</v>
       </c>
-      <c r="B318" t="n">
+      <c r="B318" s="1" t="n">
         <v>0.0049</v>
       </c>
-      <c r="C318" t="n">
+      <c r="C318" s="1" t="n">
         <v>0.0722</v>
       </c>
-      <c r="D318" t="n">
+      <c r="D318" s="1" t="n">
         <v>0.0629</v>
       </c>
-      <c r="E318" t="n">
+      <c r="E318" s="1" t="n">
         <v>0.0737</v>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" s="2" t="n">
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="4" t="n">
         <v>35582</v>
       </c>
-      <c r="B319" t="n">
+      <c r="B319" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C319" t="n">
+      <c r="C319" s="1" t="n">
         <v>0.0447</v>
       </c>
-      <c r="D319" t="n">
+      <c r="D319" s="1" t="n">
         <v>0.0452</v>
       </c>
-      <c r="E319" t="n">
+      <c r="E319" s="1" t="n">
         <v>0.0434</v>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" s="2" t="n">
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="4" t="n">
         <v>35612</v>
       </c>
-      <c r="B320" t="n">
+      <c r="B320" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C320" t="n">
+      <c r="C320" s="1" t="n">
         <v>0.0774</v>
       </c>
-      <c r="D320" t="n">
+      <c r="D320" s="1" t="n">
         <v>0.0712</v>
       </c>
-      <c r="E320" t="n">
+      <c r="E320" s="1" t="n">
         <v>0.076</v>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" s="2" t="n">
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="4" t="n">
         <v>35643</v>
       </c>
-      <c r="B321" t="n">
+      <c r="B321" s="1" t="n">
         <v>0.0041</v>
       </c>
-      <c r="C321" t="n">
+      <c r="C321" s="1" t="n">
         <v>-0.0369</v>
       </c>
-      <c r="D321" t="n">
-        <v>-0.008399999999999999</v>
-      </c>
-      <c r="E321" t="n">
+      <c r="D321" s="1" t="n">
+        <v>-0.0084</v>
+      </c>
+      <c r="E321" s="1" t="n">
         <v>-0.0488</v>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" s="2" t="n">
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="4" t="n">
         <v>35674</v>
       </c>
-      <c r="B322" t="n">
+      <c r="B322" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C322" t="n">
+      <c r="C322" s="1" t="n">
         <v>0.0578</v>
       </c>
-      <c r="D322" t="n">
+      <c r="D322" s="1" t="n">
         <v>0.067</v>
       </c>
-      <c r="E322" t="n">
+      <c r="E322" s="1" t="n">
         <v>0.0527</v>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" s="2" t="n">
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="4" t="n">
         <v>35704</v>
       </c>
-      <c r="B323" t="n">
+      <c r="B323" s="1" t="n">
         <v>0.0042</v>
       </c>
-      <c r="C323" t="n">
+      <c r="C323" s="1" t="n">
         <v>-0.0338</v>
       </c>
-      <c r="D323" t="n">
+      <c r="D323" s="1" t="n">
         <v>-0.0294</v>
       </c>
-      <c r="E323" t="n">
+      <c r="E323" s="1" t="n">
         <v>-0.0348</v>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" s="2" t="n">
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="4" t="n">
         <v>35735</v>
       </c>
-      <c r="B324" t="n">
+      <c r="B324" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C324" t="n">
+      <c r="C324" s="1" t="n">
         <v>0.0338</v>
       </c>
-      <c r="D324" t="n">
+      <c r="D324" s="1" t="n">
         <v>0.0282</v>
       </c>
-      <c r="E324" t="n">
+      <c r="E324" s="1" t="n">
         <v>0.0451</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" s="2" t="n">
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="4" t="n">
         <v>35765</v>
       </c>
-      <c r="B325" t="n">
+      <c r="B325" s="1" t="n">
         <v>0.0048</v>
       </c>
-      <c r="C325" t="n">
+      <c r="C325" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="D325" t="n">
+      <c r="D325" s="1" t="n">
         <v>0.0369</v>
       </c>
-      <c r="E325" t="n">
+      <c r="E325" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" s="2" t="n">
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="4" t="n">
         <v>35796</v>
       </c>
-      <c r="B326" t="n">
+      <c r="B326" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C326" t="n">
+      <c r="C326" s="1" t="n">
         <v>0.0058</v>
       </c>
-      <c r="D326" t="n">
+      <c r="D326" s="1" t="n">
         <v>-0.0062</v>
       </c>
-      <c r="E326" t="n">
+      <c r="E326" s="1" t="n">
         <v>0.0227</v>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" s="2" t="n">
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="4" t="n">
         <v>35827</v>
       </c>
-      <c r="B327" t="n">
+      <c r="B327" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C327" t="n">
+      <c r="C327" s="1" t="n">
         <v>0.0742</v>
       </c>
-      <c r="D327" t="n">
+      <c r="D327" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="E327" t="n">
+      <c r="E327" s="1" t="n">
         <v>0.0711</v>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" s="2" t="n">
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="4" t="n">
         <v>35855</v>
       </c>
-      <c r="B328" t="n">
+      <c r="B328" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C328" t="n">
+      <c r="C328" s="1" t="n">
         <v>0.0515</v>
       </c>
-      <c r="D328" t="n">
-        <v>0.06509999999999999</v>
-      </c>
-      <c r="E328" t="n">
+      <c r="D328" s="1" t="n">
+        <v>0.0651</v>
+      </c>
+      <c r="E328" s="1" t="n">
         <v>0.0482</v>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" s="2" t="n">
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="4" t="n">
         <v>35886</v>
       </c>
-      <c r="B329" t="n">
+      <c r="B329" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C329" t="n">
+      <c r="C329" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="D329" t="n">
+      <c r="D329" s="1" t="n">
         <v>0.0169</v>
       </c>
-      <c r="E329" t="n">
+      <c r="E329" s="1" t="n">
         <v>0.0091</v>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" s="2" t="n">
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="4" t="n">
         <v>35916</v>
       </c>
-      <c r="B330" t="n">
+      <c r="B330" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C330" t="n">
+      <c r="C330" s="1" t="n">
         <v>-0.0267</v>
       </c>
-      <c r="D330" t="n">
+      <c r="D330" s="1" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E330" t="n">
+      <c r="E330" s="1" t="n">
         <v>-0.0245</v>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" s="2" t="n">
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="4" t="n">
         <v>35947</v>
       </c>
-      <c r="B331" t="n">
+      <c r="B331" s="1" t="n">
         <v>0.0041</v>
       </c>
-      <c r="C331" t="n">
+      <c r="C331" s="1" t="n">
         <v>0.036</v>
       </c>
-      <c r="D331" t="n">
+      <c r="D331" s="1" t="n">
         <v>0.0166</v>
       </c>
-      <c r="E331" t="n">
+      <c r="E331" s="1" t="n">
         <v>0.053</v>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" s="2" t="n">
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="4" t="n">
         <v>35977</v>
       </c>
-      <c r="B332" t="n">
+      <c r="B332" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C332" t="n">
+      <c r="C332" s="1" t="n">
         <v>-0.0202</v>
       </c>
-      <c r="D332" t="n">
+      <c r="D332" s="1" t="n">
         <v>-0.0539</v>
       </c>
-      <c r="E332" t="n">
+      <c r="E332" s="1" t="n">
         <v>-0.0115</v>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" s="2" t="n">
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="4" t="n">
         <v>36008</v>
       </c>
-      <c r="B333" t="n">
+      <c r="B333" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C333" t="n">
+      <c r="C333" s="1" t="n">
         <v>-0.1562</v>
       </c>
-      <c r="D333" t="n">
+      <c r="D333" s="1" t="n">
         <v>-0.1358</v>
       </c>
-      <c r="E333" t="n">
+      <c r="E333" s="1" t="n">
         <v>-0.1414</v>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" s="2" t="n">
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="4" t="n">
         <v>36039</v>
       </c>
-      <c r="B334" t="n">
+      <c r="B334" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C334" t="n">
+      <c r="C334" s="1" t="n">
         <v>0.0665</v>
       </c>
-      <c r="D334" t="n">
-        <v>0.05860000000000001</v>
-      </c>
-      <c r="E334" t="n">
+      <c r="D334" s="1" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="E334" s="1" t="n">
         <v>0.0793</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" s="2" t="n">
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="4" t="n">
         <v>36069</v>
       </c>
-      <c r="B335" t="n">
+      <c r="B335" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="C335" t="n">
+      <c r="C335" s="1" t="n">
         <v>0.073</v>
       </c>
-      <c r="D335" t="n">
+      <c r="D335" s="1" t="n">
         <v>0.0432</v>
       </c>
-      <c r="E335" t="n">
+      <c r="E335" s="1" t="n">
         <v>0.0788</v>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" s="2" t="n">
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="4" t="n">
         <v>36100</v>
       </c>
-      <c r="B336" t="n">
+      <c r="B336" s="1" t="n">
         <v>0.0031</v>
       </c>
-      <c r="C336" t="n">
+      <c r="C336" s="1" t="n">
         <v>0.0638</v>
       </c>
-      <c r="D336" t="n">
+      <c r="D336" s="1" t="n">
         <v>0.0435</v>
       </c>
-      <c r="E336" t="n">
+      <c r="E336" s="1" t="n">
         <v>0.0707</v>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" s="2" t="n">
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="4" t="n">
         <v>36130</v>
       </c>
-      <c r="B337" t="n">
+      <c r="B337" s="1" t="n">
         <v>0.0038</v>
       </c>
-      <c r="C337" t="n">
+      <c r="C337" s="1" t="n">
         <v>0.0653</v>
       </c>
-      <c r="D337" t="n">
+      <c r="D337" s="1" t="n">
         <v>0.0356</v>
       </c>
-      <c r="E337" t="n">
-        <v>0.08160000000000001</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="E337" s="1" t="n">
+        <v>0.0816</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="4" t="n">
         <v>36161</v>
       </c>
-      <c r="B338" t="n">
+      <c r="B338" s="1" t="n">
         <v>0.0035</v>
       </c>
-      <c r="C338" t="n">
+      <c r="C338" s="1" t="n">
         <v>0.0383</v>
       </c>
-      <c r="D338" t="n">
-        <v>-0.009000000000000001</v>
-      </c>
-      <c r="E338" t="n">
+      <c r="D338" s="1" t="n">
+        <v>-0.009</v>
+      </c>
+      <c r="E338" s="1" t="n">
         <v>0.0491</v>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" s="2" t="n">
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="4" t="n">
         <v>36192</v>
       </c>
-      <c r="B339" t="n">
+      <c r="B339" s="1" t="n">
         <v>0.0035</v>
       </c>
-      <c r="C339" t="n">
+      <c r="C339" s="1" t="n">
         <v>-0.0373</v>
       </c>
-      <c r="D339" t="n">
+      <c r="D339" s="1" t="n">
         <v>-0.0263</v>
       </c>
-      <c r="E339" t="n">
+      <c r="E339" s="1" t="n">
         <v>-0.0467</v>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" s="2" t="n">
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="4" t="n">
         <v>36220</v>
       </c>
-      <c r="B340" t="n">
+      <c r="B340" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C340" t="n">
+      <c r="C340" s="1" t="n">
         <v>0.0391</v>
       </c>
-      <c r="D340" t="n">
+      <c r="D340" s="1" t="n">
         <v>0.0036</v>
       </c>
-      <c r="E340" t="n">
+      <c r="E340" s="1" t="n">
         <v>0.0385</v>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" s="2" t="n">
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="4" t="n">
         <v>36251</v>
       </c>
-      <c r="B341" t="n">
+      <c r="B341" s="1" t="n">
         <v>0.0037</v>
       </c>
-      <c r="C341" t="n">
+      <c r="C341" s="1" t="n">
         <v>0.0471</v>
       </c>
-      <c r="D341" t="n">
+      <c r="D341" s="1" t="n">
         <v>0.0747</v>
       </c>
-      <c r="E341" t="n">
+      <c r="E341" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" s="2" t="n">
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="4" t="n">
         <v>36281</v>
       </c>
-      <c r="B342" t="n">
+      <c r="B342" s="1" t="n">
         <v>0.0034</v>
       </c>
-      <c r="C342" t="n">
+      <c r="C342" s="1" t="n">
         <v>-0.0212</v>
       </c>
-      <c r="D342" t="n">
+      <c r="D342" s="1" t="n">
         <v>0.0097</v>
       </c>
-      <c r="E342" t="n">
+      <c r="E342" s="1" t="n">
         <v>-0.0242</v>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" s="2" t="n">
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="4" t="n">
         <v>36312</v>
       </c>
-      <c r="B343" t="n">
+      <c r="B343" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C343" t="n">
+      <c r="C343" s="1" t="n">
         <v>0.0517</v>
       </c>
-      <c r="D343" t="n">
+      <c r="D343" s="1" t="n">
         <v>0.0147</v>
       </c>
-      <c r="E343" t="n">
-        <v>0.06509999999999999</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="E343" s="1" t="n">
+        <v>0.0651</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="4" t="n">
         <v>36342</v>
       </c>
-      <c r="B344" t="n">
+      <c r="B344" s="1" t="n">
         <v>0.0038</v>
       </c>
-      <c r="C344" t="n">
+      <c r="C344" s="1" t="n">
         <v>-0.0311</v>
       </c>
-      <c r="D344" t="n">
+      <c r="D344" s="1" t="n">
         <v>-0.0238</v>
       </c>
-      <c r="E344" t="n">
+      <c r="E344" s="1" t="n">
         <v>-0.0297</v>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" s="2" t="n">
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="4" t="n">
         <v>36373</v>
       </c>
-      <c r="B345" t="n">
+      <c r="B345" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C345" t="n">
+      <c r="C345" s="1" t="n">
         <v>-0.0098</v>
       </c>
-      <c r="D345" t="n">
+      <c r="D345" s="1" t="n">
         <v>-0.0318</v>
       </c>
-      <c r="E345" t="n">
+      <c r="E345" s="1" t="n">
         <v>-0.0003</v>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" s="2" t="n">
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="4" t="n">
         <v>36404</v>
       </c>
-      <c r="B346" t="n">
+      <c r="B346" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C346" t="n">
+      <c r="C346" s="1" t="n">
         <v>-0.0238</v>
       </c>
-      <c r="D346" t="n">
+      <c r="D346" s="1" t="n">
         <v>-0.0354</v>
       </c>
-      <c r="E346" t="n">
+      <c r="E346" s="1" t="n">
         <v>-0.018</v>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" s="2" t="n">
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="4" t="n">
         <v>36434</v>
       </c>
-      <c r="B347" t="n">
+      <c r="B347" s="1" t="n">
         <v>0.0039</v>
       </c>
-      <c r="C347" t="n">
+      <c r="C347" s="1" t="n">
         <v>0.0648</v>
       </c>
-      <c r="D347" t="n">
+      <c r="D347" s="1" t="n">
         <v>0.0142</v>
       </c>
-      <c r="E347" t="n">
-        <v>0.06419999999999999</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="E347" s="1" t="n">
+        <v>0.0642</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="4" t="n">
         <v>36465</v>
       </c>
-      <c r="B348" t="n">
+      <c r="B348" s="1" t="n">
         <v>0.0036</v>
       </c>
-      <c r="C348" t="n">
+      <c r="C348" s="1" t="n">
         <v>0.0377</v>
       </c>
-      <c r="D348" t="n">
+      <c r="D348" s="1" t="n">
         <v>0.0283</v>
       </c>
-      <c r="E348" t="n">
+      <c r="E348" s="1" t="n">
         <v>0.0443</v>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" s="2" t="n">
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="4" t="n">
         <v>36495</v>
       </c>
-      <c r="B349" t="n">
+      <c r="B349" s="1" t="n">
         <v>0.0044</v>
       </c>
-      <c r="C349" t="n">
+      <c r="C349" s="1" t="n">
         <v>0.081</v>
       </c>
-      <c r="D349" t="n">
+      <c r="D349" s="1" t="n">
         <v>0.0517</v>
       </c>
-      <c r="E349" t="n">
-        <v>0.08470000000000001</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="E349" s="1" t="n">
+        <v>0.0847</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="4" t="n">
         <v>36526</v>
       </c>
-      <c r="B350" t="n">
+      <c r="B350" s="1" t="n">
         <v>0.0041</v>
       </c>
-      <c r="C350" t="n">
+      <c r="C350" s="1" t="n">
         <v>-0.0433</v>
       </c>
-      <c r="D350" t="n">
+      <c r="D350" s="1" t="n">
         <v>-0.0342</v>
       </c>
-      <c r="E350" t="n">
+      <c r="E350" s="1" t="n">
         <v>-0.0454</v>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" s="2" t="n">
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="4" t="n">
         <v>36557</v>
       </c>
-      <c r="B351" t="n">
+      <c r="B351" s="1" t="n">
         <v>0.0043</v>
       </c>
-      <c r="C351" t="n">
+      <c r="C351" s="1" t="n">
         <v>0.0289</v>
       </c>
-      <c r="D351" t="n">
+      <c r="D351" s="1" t="n">
         <v>0.0397</v>
       </c>
-      <c r="E351" t="n">
+      <c r="E351" s="1" t="n">
         <v>0.0211</v>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" s="2" t="n">
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="4" t="n">
         <v>36586</v>
       </c>
-      <c r="B352" t="n">
+      <c r="B352" s="1" t="n">
         <v>0.0047</v>
       </c>
-      <c r="C352" t="n">
+      <c r="C352" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="D352" t="n">
+      <c r="D352" s="1" t="n">
         <v>0.0674</v>
       </c>
-      <c r="E352" t="n">
-        <v>0.07780000000000001</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="E352" s="1" t="n">
+        <v>0.0778</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="4" t="n">
         <v>36617</v>
       </c>
-      <c r="B353" t="n">
+      <c r="B353" s="1" t="n">
         <v>0.0046</v>
       </c>
-      <c r="C353" t="n">
+      <c r="C353" s="1" t="n">
         <v>-0.0593</v>
       </c>
-      <c r="D353" t="n">
+      <c r="D353" s="1" t="n">
         <v>-0.0295</v>
       </c>
-      <c r="E353" t="n">
+      <c r="E353" s="1" t="n">
         <v>-0.0452</v>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" s="2" t="n">
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="4" t="n">
         <v>36647</v>
       </c>
-      <c r="B354" t="n">
+      <c r="B354" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="C354" t="n">
+      <c r="C354" s="1" t="n">
         <v>-0.0389</v>
       </c>
-      <c r="D354" t="n">
+      <c r="D354" s="1" t="n">
         <v>-0.0002</v>
       </c>
-      <c r="E354" t="n">
+      <c r="E354" s="1" t="n">
         <v>-0.0361</v>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" s="2" t="n">
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A355" s="4" t="n">
         <v>36678</v>
       </c>
-      <c r="B355" t="n">
+      <c r="B355" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="C355" t="n">
+      <c r="C355" s="1" t="n">
         <v>0.0508</v>
       </c>
-      <c r="D355" t="n">
+      <c r="D355" s="1" t="n">
         <v>0.0178</v>
       </c>
-      <c r="E355" t="n">
+      <c r="E355" s="1" t="n">
         <v>0.0503</v>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" s="2" t="n">
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="4" t="n">
         <v>36708</v>
       </c>
-      <c r="B356" t="n">
+      <c r="B356" s="1" t="n">
         <v>0.0048</v>
       </c>
-      <c r="C356" t="n">
+      <c r="C356" s="1" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D356" t="n">
+      <c r="D356" s="1" t="n">
         <v>0.0357</v>
       </c>
-      <c r="E356" t="n">
+      <c r="E356" s="1" t="n">
         <v>-0.0304</v>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" s="2" t="n">
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="4" t="n">
         <v>36739</v>
       </c>
-      <c r="B357" t="n">
+      <c r="B357" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="C357" t="n">
-        <v>0.07530000000000001</v>
-      </c>
-      <c r="D357" t="n">
+      <c r="C357" s="1" t="n">
+        <v>0.0753</v>
+      </c>
+      <c r="D357" s="1" t="n">
         <v>0.0684</v>
       </c>
-      <c r="E357" t="n">
-        <v>0.07539999999999999</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="E357" s="1" t="n">
+        <v>0.0754</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="4" t="n">
         <v>36770</v>
       </c>
-      <c r="B358" t="n">
+      <c r="B358" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="C358" t="n">
+      <c r="C358" s="1" t="n">
         <v>-0.0493</v>
       </c>
-      <c r="D358" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-      <c r="E358" t="n">
+      <c r="D358" s="1" t="n">
+        <v>0.0088</v>
+      </c>
+      <c r="E358" s="1" t="n">
         <v>-0.0597</v>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" s="2" t="n">
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="4" t="n">
         <v>36800</v>
       </c>
-      <c r="B359" t="n">
+      <c r="B359" s="1" t="n">
         <v>0.0056</v>
       </c>
-      <c r="C359" t="n">
+      <c r="C359" s="1" t="n">
         <v>-0.0222</v>
       </c>
-      <c r="D359" t="n">
+      <c r="D359" s="1" t="n">
         <v>0.0118</v>
       </c>
-      <c r="E359" t="n">
+      <c r="E359" s="1" t="n">
         <v>-0.0211</v>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" s="2" t="n">
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="4" t="n">
         <v>36831</v>
       </c>
-      <c r="B360" t="n">
+      <c r="B360" s="1" t="n">
         <v>0.0051</v>
       </c>
-      <c r="C360" t="n">
+      <c r="C360" s="1" t="n">
         <v>-0.1019</v>
       </c>
-      <c r="D360" t="n">
-        <v>-0.007800000000000001</v>
-      </c>
-      <c r="E360" t="n">
+      <c r="D360" s="1" t="n">
+        <v>-0.0078</v>
+      </c>
+      <c r="E360" s="1" t="n">
         <v>-0.1071</v>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" s="2" t="n">
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="4" t="n">
         <v>36861</v>
       </c>
-      <c r="B361" t="n">
+      <c r="B361" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="C361" t="n">
+      <c r="C361" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="D361" t="n">
+      <c r="D361" s="1" t="n">
         <v>0.0872</v>
       </c>
-      <c r="E361" t="n">
+      <c r="E361" s="1" t="n">
         <v>-0.0025</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>